--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">artist</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.247</t>
+    <t xml:space="preserve">EA 23.252</t>
   </si>
   <si>
     <t xml:space="preserve">"You senseless bastard!"

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="1102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="1103">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">artist</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.281</t>
   </si>
   <si>
     <t xml:space="preserve">"You senseless bastard!"
@@ -3422,79 +3422,82 @@
     <t xml:space="preserve">Alpha 20.64</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beta 22.86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beta 22.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 20.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 20.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 20.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.209 Patch 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 20.66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.61 fix 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 20.69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 14.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 21.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 20.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.92 Patch 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 12.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 15.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 20.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.229 Patch 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.237 Patch 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beta 22.86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beta 22.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 20.49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 20.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 20.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.209 Patch 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 20.66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.61 fix 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 20.69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 14.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 21.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 20.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.92 Patch 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 12.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 15.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 20.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.229 Patch 3</t>
   </si>
   <si>
     <t xml:space="preserve">EA 23.187</t>
@@ -5187,7 +5190,7 @@
       <c r="G3"/>
       <c r="H3"/>
       <c r="I3" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -5196,7 +5199,7 @@
         <v>20</v>
       </c>
       <c r="L3" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="M3" t="s">
         <v>21</v>
@@ -5205,7 +5208,7 @@
         <v>22</v>
       </c>
       <c r="O3" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="P3" t="s">
         <v>23</v>
@@ -5222,7 +5225,7 @@
         <v>756</v>
       </c>
       <c r="C4" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D4" t="s">
         <v>26</v>
@@ -5233,7 +5236,7 @@
       <c r="G4"/>
       <c r="H4"/>
       <c r="I4" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="J4" t="s">
         <v>26</v>
@@ -5242,7 +5245,7 @@
         <v>27</v>
       </c>
       <c r="L4" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="M4" t="s">
         <v>28</v>
@@ -5261,7 +5264,7 @@
         <v>757</v>
       </c>
       <c r="C5" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D5" t="s">
         <v>31</v>
@@ -5283,10 +5286,10 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>758</v>
       </c>
       <c r="C6" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D6" t="s">
         <v>34</v>
@@ -5299,7 +5302,7 @@
       <c r="J6"/>
       <c r="K6"/>
       <c r="L6" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="M6" t="s">
         <v>36</v>
@@ -5308,7 +5311,7 @@
         <v>37</v>
       </c>
       <c r="O6" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="P6" t="s">
         <v>38</v>
@@ -5325,7 +5328,7 @@
         <v>755</v>
       </c>
       <c r="C7" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D7" t="s">
         <v>41</v>
@@ -5336,7 +5339,7 @@
       <c r="G7"/>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="J7" t="s">
         <v>43</v>
@@ -5345,7 +5348,7 @@
         <v>44</v>
       </c>
       <c r="L7" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="M7" t="s">
         <v>45</v>
@@ -5364,7 +5367,7 @@
         <v>755</v>
       </c>
       <c r="C8" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D8" t="s">
         <v>48</v>
@@ -5375,7 +5378,7 @@
       <c r="G8"/>
       <c r="H8"/>
       <c r="I8" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="J8" t="s">
         <v>50</v>
@@ -5384,7 +5387,7 @@
         <v>51</v>
       </c>
       <c r="L8" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="M8" t="s">
         <v>52</v>
@@ -5393,7 +5396,7 @@
         <v>53</v>
       </c>
       <c r="O8" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="P8" t="s">
         <v>54</v>
@@ -5410,7 +5413,7 @@
         <v>755</v>
       </c>
       <c r="C9" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -5421,7 +5424,7 @@
       <c r="G9"/>
       <c r="H9"/>
       <c r="I9" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="J9" t="s">
         <v>59</v>
@@ -5430,7 +5433,7 @@
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="M9" t="s">
         <v>61</v>
@@ -5439,7 +5442,7 @@
         <v>62</v>
       </c>
       <c r="O9" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="P9" t="s">
         <v>63</v>
@@ -5456,7 +5459,7 @@
         <v>755</v>
       </c>
       <c r="C10" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D10" t="s">
         <v>66</v>
@@ -5467,21 +5470,21 @@
       <c r="G10"/>
       <c r="H10"/>
       <c r="I10" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="J10"/>
       <c r="K10" t="s">
         <v>68</v>
       </c>
       <c r="L10" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M10"/>
       <c r="N10" t="s">
         <v>69</v>
       </c>
       <c r="O10" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="P10"/>
       <c r="Q10" t="s">
@@ -5496,7 +5499,7 @@
         <v>759</v>
       </c>
       <c r="C11" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D11" t="s">
         <v>72</v>
@@ -5507,7 +5510,7 @@
       <c r="G11"/>
       <c r="H11"/>
       <c r="I11" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="J11" t="s">
         <v>74</v>
@@ -5516,7 +5519,7 @@
         <v>75</v>
       </c>
       <c r="L11" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="M11" t="s">
         <v>76</v>
@@ -5525,7 +5528,7 @@
         <v>77</v>
       </c>
       <c r="O11" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="P11" t="s">
         <v>78</v>
@@ -5542,7 +5545,7 @@
         <v>760</v>
       </c>
       <c r="C12" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D12" t="s">
         <v>81</v>
@@ -5553,7 +5556,7 @@
       <c r="G12"/>
       <c r="H12"/>
       <c r="I12" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="J12" t="s">
         <v>83</v>
@@ -5562,7 +5565,7 @@
         <v>84</v>
       </c>
       <c r="L12" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="M12" t="s">
         <v>85</v>
@@ -5571,7 +5574,7 @@
         <v>86</v>
       </c>
       <c r="O12" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="P12" t="s">
         <v>87</v>
@@ -5588,7 +5591,7 @@
         <v>757</v>
       </c>
       <c r="C13" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D13" t="s">
         <v>90</v>
@@ -5606,7 +5609,7 @@
         <v>92</v>
       </c>
       <c r="L13" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="M13" t="s">
         <v>93</v>
@@ -5622,10 +5625,10 @@
         <v>95</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>758</v>
       </c>
       <c r="C14" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D14" t="s">
         <v>96</v>
@@ -5636,7 +5639,7 @@
       <c r="G14"/>
       <c r="H14"/>
       <c r="I14" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="J14" t="s">
         <v>74</v>
@@ -5645,7 +5648,7 @@
         <v>98</v>
       </c>
       <c r="L14" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="M14" t="s">
         <v>76</v>
@@ -5654,7 +5657,7 @@
         <v>99</v>
       </c>
       <c r="O14" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="P14" t="s">
         <v>78</v>
@@ -5671,7 +5674,7 @@
         <v>761</v>
       </c>
       <c r="C15" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D15" t="s">
         <v>102</v>
@@ -5714,7 +5717,7 @@
       <c r="G16"/>
       <c r="H16"/>
       <c r="I16" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="J16" t="s">
         <v>106</v>
@@ -5723,7 +5726,7 @@
         <v>107</v>
       </c>
       <c r="L16" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M16" t="s">
         <v>108</v>
@@ -5732,7 +5735,7 @@
         <v>109</v>
       </c>
       <c r="O16" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="P16" t="s">
         <v>110</v>
@@ -5749,7 +5752,7 @@
         <v>763</v>
       </c>
       <c r="C17" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D17" t="s">
         <v>113</v>
@@ -5760,7 +5763,7 @@
       <c r="G17"/>
       <c r="H17"/>
       <c r="I17" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="J17" t="s">
         <v>113</v>
@@ -5769,7 +5772,7 @@
         <v>114</v>
       </c>
       <c r="L17" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="M17" t="s">
         <v>113</v>
@@ -5778,7 +5781,7 @@
         <v>114</v>
       </c>
       <c r="O17" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="P17" t="s">
         <v>113</v>
@@ -5799,7 +5802,7 @@
       <c r="G18"/>
       <c r="H18"/>
       <c r="I18" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="J18" t="s">
         <v>116</v>
@@ -5808,7 +5811,7 @@
         <v>117</v>
       </c>
       <c r="L18" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="M18" t="s">
         <v>118</v>
@@ -5817,7 +5820,7 @@
         <v>119</v>
       </c>
       <c r="O18" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="P18" t="s">
         <v>120</v>
@@ -5838,7 +5841,7 @@
       <c r="G19"/>
       <c r="H19"/>
       <c r="I19" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="J19" t="s">
         <v>116</v>
@@ -5847,7 +5850,7 @@
         <v>117</v>
       </c>
       <c r="L19" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="M19" t="s">
         <v>123</v>
@@ -5856,7 +5859,7 @@
         <v>124</v>
       </c>
       <c r="O19" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="P19" t="s">
         <v>125</v>
@@ -5873,7 +5876,7 @@
         <v>755</v>
       </c>
       <c r="C20" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D20" t="s">
         <v>128</v>
@@ -5884,7 +5887,7 @@
       <c r="G20"/>
       <c r="H20"/>
       <c r="I20" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="J20" t="s">
         <v>130</v>
@@ -5893,7 +5896,7 @@
         <v>131</v>
       </c>
       <c r="L20" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="M20" t="s">
         <v>132</v>
@@ -5902,7 +5905,7 @@
         <v>133</v>
       </c>
       <c r="O20" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="P20" t="s">
         <v>134</v>
@@ -5923,7 +5926,7 @@
       <c r="G21"/>
       <c r="H21"/>
       <c r="I21" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="J21" t="s">
         <v>137</v>
@@ -5932,7 +5935,7 @@
         <v>138</v>
       </c>
       <c r="L21" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="M21" t="s">
         <v>139</v>
@@ -5941,7 +5944,7 @@
         <v>140</v>
       </c>
       <c r="O21" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="P21" t="s">
         <v>141</v>
@@ -5962,7 +5965,7 @@
       <c r="G22"/>
       <c r="H22"/>
       <c r="I22" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="J22" t="s">
         <v>144</v>
@@ -5971,7 +5974,7 @@
         <v>145</v>
       </c>
       <c r="L22" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="M22" t="s">
         <v>146</v>
@@ -5980,7 +5983,7 @@
         <v>147</v>
       </c>
       <c r="O22" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="P22" t="s">
         <v>148</v>
@@ -5997,7 +6000,7 @@
         <v>759</v>
       </c>
       <c r="C23" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D23" t="s">
         <v>151</v>
@@ -6022,7 +6025,7 @@
         <v>755</v>
       </c>
       <c r="C24" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D24" t="s">
         <v>154</v>
@@ -6033,7 +6036,7 @@
       <c r="G24"/>
       <c r="H24"/>
       <c r="I24" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="J24" t="s">
         <v>156</v>
@@ -6042,7 +6045,7 @@
         <v>157</v>
       </c>
       <c r="L24" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M24" t="s">
         <v>158</v>
@@ -6051,7 +6054,7 @@
         <v>159</v>
       </c>
       <c r="O24" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="P24" t="s">
         <v>160</v>
@@ -6072,7 +6075,7 @@
       <c r="G25"/>
       <c r="H25"/>
       <c r="I25" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="J25" t="s">
         <v>163</v>
@@ -6100,7 +6103,7 @@
         <v>764</v>
       </c>
       <c r="C26" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D26" t="s">
         <v>167</v>
@@ -6111,7 +6114,7 @@
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="J26" t="s">
         <v>167</v>
@@ -6132,7 +6135,7 @@
         <v>765</v>
       </c>
       <c r="C27" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D27" t="s">
         <v>170</v>
@@ -6141,7 +6144,7 @@
         <v>171</v>
       </c>
       <c r="F27" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G27" t="s">
         <v>170</v>
@@ -6164,7 +6167,7 @@
         <v>755</v>
       </c>
       <c r="C28" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D28" t="s">
         <v>173</v>
@@ -6177,7 +6180,7 @@
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="M28" t="s">
         <v>175</v>
@@ -6186,7 +6189,7 @@
         <v>176</v>
       </c>
       <c r="O28" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="P28" t="s">
         <v>177</v>
@@ -6207,7 +6210,7 @@
       <c r="G29"/>
       <c r="H29"/>
       <c r="I29" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="J29" t="s">
         <v>180</v>
@@ -6216,7 +6219,7 @@
         <v>181</v>
       </c>
       <c r="L29" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="M29" t="s">
         <v>182</v>
@@ -6225,7 +6228,7 @@
         <v>183</v>
       </c>
       <c r="O29" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="P29" t="s">
         <v>184</v>
@@ -6242,7 +6245,7 @@
         <v>766</v>
       </c>
       <c r="C30" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D30" t="s">
         <v>187</v>
@@ -6253,7 +6256,7 @@
       <c r="G30"/>
       <c r="H30"/>
       <c r="I30" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="J30" t="s">
         <v>189</v>
@@ -6262,7 +6265,7 @@
         <v>190</v>
       </c>
       <c r="L30" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="M30" t="s">
         <v>191</v>
@@ -6271,7 +6274,7 @@
         <v>192</v>
       </c>
       <c r="O30" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="P30" t="s">
         <v>193</v>
@@ -6288,7 +6291,7 @@
         <v>767</v>
       </c>
       <c r="C31" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D31" t="s">
         <v>196</v>
@@ -6299,7 +6302,7 @@
       <c r="G31"/>
       <c r="H31"/>
       <c r="I31" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="J31" t="s">
         <v>189</v>
@@ -6308,7 +6311,7 @@
         <v>190</v>
       </c>
       <c r="L31" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="M31" t="s">
         <v>191</v>
@@ -6317,7 +6320,7 @@
         <v>192</v>
       </c>
       <c r="O31" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="P31" t="s">
         <v>193</v>
@@ -6334,7 +6337,7 @@
         <v>767</v>
       </c>
       <c r="C32" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D32" t="s">
         <v>199</v>
@@ -6345,7 +6348,7 @@
       <c r="G32"/>
       <c r="H32"/>
       <c r="I32" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="J32" t="s">
         <v>189</v>
@@ -6354,7 +6357,7 @@
         <v>190</v>
       </c>
       <c r="L32" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="M32" t="s">
         <v>191</v>
@@ -6363,7 +6366,7 @@
         <v>192</v>
       </c>
       <c r="O32" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="P32" t="s">
         <v>193</v>
@@ -6380,7 +6383,7 @@
         <v>767</v>
       </c>
       <c r="C33" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D33" t="s">
         <v>202</v>
@@ -6391,7 +6394,7 @@
       <c r="G33"/>
       <c r="H33"/>
       <c r="I33" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="J33" t="s">
         <v>204</v>
@@ -6400,7 +6403,7 @@
         <v>205</v>
       </c>
       <c r="L33" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="M33" t="s">
         <v>206</v>
@@ -6409,7 +6412,7 @@
         <v>207</v>
       </c>
       <c r="O33" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="P33" t="s">
         <v>208</v>
@@ -6426,7 +6429,7 @@
         <v>755</v>
       </c>
       <c r="C34" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D34" t="s">
         <v>211</v>
@@ -6437,7 +6440,7 @@
       <c r="G34"/>
       <c r="H34"/>
       <c r="I34" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="J34" t="s">
         <v>213</v>
@@ -6446,7 +6449,7 @@
         <v>214</v>
       </c>
       <c r="L34" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="M34" t="s">
         <v>215</v>
@@ -6455,7 +6458,7 @@
         <v>216</v>
       </c>
       <c r="O34" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="P34" t="s">
         <v>217</v>
@@ -6478,7 +6481,7 @@
       <c r="J35"/>
       <c r="K35"/>
       <c r="L35" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="M35" t="s">
         <v>220</v>
@@ -6487,7 +6490,7 @@
         <v>221</v>
       </c>
       <c r="O35" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="P35" t="s">
         <v>222</v>
@@ -6508,7 +6511,7 @@
       <c r="G36"/>
       <c r="H36"/>
       <c r="I36" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="J36" t="s">
         <v>225</v>
@@ -6517,7 +6520,7 @@
         <v>226</v>
       </c>
       <c r="L36" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="M36" t="s">
         <v>227</v>
@@ -6526,7 +6529,7 @@
         <v>228</v>
       </c>
       <c r="O36" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="P36" t="s">
         <v>229</v>
@@ -6545,7 +6548,7 @@
       <c r="D37"/>
       <c r="E37"/>
       <c r="F37" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G37" t="s">
         <v>232</v>
@@ -6554,7 +6557,7 @@
         <v>233</v>
       </c>
       <c r="I37" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="J37" t="s">
         <v>234</v>
@@ -6563,7 +6566,7 @@
         <v>235</v>
       </c>
       <c r="L37" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="M37" t="s">
         <v>236</v>
@@ -6572,7 +6575,7 @@
         <v>237</v>
       </c>
       <c r="O37" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="P37" t="s">
         <v>238</v>
@@ -6589,7 +6592,7 @@
         <v>768</v>
       </c>
       <c r="C38" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D38" t="s">
         <v>241</v>
@@ -6642,7 +6645,7 @@
         <v>769</v>
       </c>
       <c r="C39" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D39" t="s">
         <v>245</v>
@@ -6651,7 +6654,7 @@
         <v>246</v>
       </c>
       <c r="F39" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="G39" t="s">
         <v>247</v>
@@ -6660,7 +6663,7 @@
         <v>248</v>
       </c>
       <c r="I39" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="J39" t="s">
         <v>234</v>
@@ -6669,7 +6672,7 @@
         <v>235</v>
       </c>
       <c r="L39" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="M39" t="s">
         <v>236</v>
@@ -6678,7 +6681,7 @@
         <v>237</v>
       </c>
       <c r="O39" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="P39" t="s">
         <v>238</v>
@@ -6695,7 +6698,7 @@
         <v>755</v>
       </c>
       <c r="C40" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D40" t="s">
         <v>250</v>
@@ -6738,7 +6741,7 @@
         <v>759</v>
       </c>
       <c r="C42" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D42" t="s">
         <v>254</v>
@@ -6749,7 +6752,7 @@
       <c r="G42"/>
       <c r="H42"/>
       <c r="I42" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="J42" t="s">
         <v>256</v>
@@ -6758,7 +6761,7 @@
         <v>257</v>
       </c>
       <c r="L42" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="M42" t="s">
         <v>258</v>
@@ -6767,7 +6770,7 @@
         <v>259</v>
       </c>
       <c r="O42" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="P42" t="s">
         <v>260</v>
@@ -6784,7 +6787,7 @@
         <v>755</v>
       </c>
       <c r="C43" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D43" t="s">
         <v>263</v>
@@ -6795,7 +6798,7 @@
       <c r="G43"/>
       <c r="H43"/>
       <c r="I43" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="J43" t="s">
         <v>265</v>
@@ -6804,7 +6807,7 @@
         <v>266</v>
       </c>
       <c r="L43" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="M43" t="s">
         <v>267</v>
@@ -6813,7 +6816,7 @@
         <v>268</v>
       </c>
       <c r="O43" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="P43" t="s">
         <v>269</v>
@@ -6834,7 +6837,7 @@
       <c r="G44"/>
       <c r="H44"/>
       <c r="I44" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="J44" t="s">
         <v>272</v>
@@ -6843,7 +6846,7 @@
         <v>273</v>
       </c>
       <c r="L44" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="M44" t="s">
         <v>274</v>
@@ -6852,7 +6855,7 @@
         <v>275</v>
       </c>
       <c r="O44" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="P44"/>
       <c r="Q44" t="s">
@@ -6871,7 +6874,7 @@
       <c r="G45"/>
       <c r="H45"/>
       <c r="I45" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="J45" t="s">
         <v>278</v>
@@ -6880,7 +6883,7 @@
         <v>279</v>
       </c>
       <c r="L45" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="M45" t="s">
         <v>280</v>
@@ -6889,7 +6892,7 @@
         <v>281</v>
       </c>
       <c r="O45" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="P45" t="s">
         <v>282</v>
@@ -6912,7 +6915,7 @@
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="M46" t="s">
         <v>285</v>
@@ -6921,7 +6924,7 @@
         <v>286</v>
       </c>
       <c r="O46" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="P46" t="s">
         <v>287</v>
@@ -6951,7 +6954,7 @@
       <c r="J47"/>
       <c r="K47"/>
       <c r="L47" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M47" t="s">
         <v>292</v>
@@ -6960,7 +6963,7 @@
         <v>293</v>
       </c>
       <c r="O47" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="P47" t="s">
         <v>294</v>
@@ -6977,7 +6980,7 @@
         <v>770</v>
       </c>
       <c r="C48" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D48" t="s">
         <v>297</v>
@@ -6988,7 +6991,7 @@
       <c r="G48"/>
       <c r="H48"/>
       <c r="I48" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="J48" t="s">
         <v>297</v>
@@ -6997,7 +7000,7 @@
         <v>298</v>
       </c>
       <c r="L48" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="M48" t="s">
         <v>297</v>
@@ -7006,7 +7009,7 @@
         <v>298</v>
       </c>
       <c r="O48" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="P48" t="s">
         <v>297</v>
@@ -7023,7 +7026,7 @@
         <v>759</v>
       </c>
       <c r="C49" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D49" t="s">
         <v>300</v>
@@ -7034,7 +7037,7 @@
       <c r="G49"/>
       <c r="H49"/>
       <c r="I49" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="J49" t="s">
         <v>302</v>
@@ -7043,7 +7046,7 @@
         <v>303</v>
       </c>
       <c r="L49" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M49" t="s">
         <v>304</v>
@@ -7052,7 +7055,7 @@
         <v>305</v>
       </c>
       <c r="O49" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="P49" t="s">
         <v>294</v>
@@ -7069,7 +7072,7 @@
         <v>755</v>
       </c>
       <c r="C50" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D50" t="s">
         <v>307</v>
@@ -7080,7 +7083,7 @@
       <c r="G50"/>
       <c r="H50"/>
       <c r="I50" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="J50" t="s">
         <v>309</v>
@@ -7089,7 +7092,7 @@
         <v>310</v>
       </c>
       <c r="L50" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="M50" t="s">
         <v>311</v>
@@ -7098,7 +7101,7 @@
         <v>312</v>
       </c>
       <c r="O50" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="P50" t="s">
         <v>313</v>
@@ -7115,7 +7118,7 @@
         <v>759</v>
       </c>
       <c r="C51" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D51" t="s">
         <v>316</v>
@@ -7126,7 +7129,7 @@
       <c r="G51"/>
       <c r="H51"/>
       <c r="I51" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="J51" t="s">
         <v>318</v>
@@ -7135,7 +7138,7 @@
         <v>319</v>
       </c>
       <c r="L51" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="M51" t="s">
         <v>320</v>
@@ -7144,7 +7147,7 @@
         <v>321</v>
       </c>
       <c r="O51" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="P51" t="s">
         <v>320</v>
@@ -7165,7 +7168,7 @@
       <c r="G52"/>
       <c r="H52"/>
       <c r="I52" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="J52" t="s">
         <v>323</v>
@@ -7174,7 +7177,7 @@
         <v>324</v>
       </c>
       <c r="L52" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="M52" t="s">
         <v>325</v>
@@ -7183,7 +7186,7 @@
         <v>326</v>
       </c>
       <c r="O52" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="P52" t="s">
         <v>327</v>
@@ -7200,7 +7203,7 @@
         <v>771</v>
       </c>
       <c r="C53" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D53" t="s">
         <v>330</v>
@@ -7246,7 +7249,7 @@
         <v>766</v>
       </c>
       <c r="C54" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D54" t="s">
         <v>334</v>
@@ -7292,7 +7295,7 @@
         <v>771</v>
       </c>
       <c r="C55" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D55" t="s">
         <v>337</v>
@@ -7338,7 +7341,7 @@
         <v>771</v>
       </c>
       <c r="C56" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D56" t="s">
         <v>340</v>
@@ -7384,7 +7387,7 @@
         <v>757</v>
       </c>
       <c r="C57" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D57" t="s">
         <v>343</v>
@@ -7395,7 +7398,7 @@
       <c r="G57"/>
       <c r="H57"/>
       <c r="I57" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="J57" t="s">
         <v>345</v>
@@ -7404,7 +7407,7 @@
         <v>346</v>
       </c>
       <c r="L57" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="M57" t="s">
         <v>347</v>
@@ -7413,7 +7416,7 @@
         <v>348</v>
       </c>
       <c r="O57" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="P57" t="s">
         <v>349</v>
@@ -7434,7 +7437,7 @@
       <c r="G58"/>
       <c r="H58"/>
       <c r="I58" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="J58" t="s">
         <v>352</v>
@@ -7443,7 +7446,7 @@
         <v>353</v>
       </c>
       <c r="L58" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="M58" t="s">
         <v>354</v>
@@ -7452,7 +7455,7 @@
         <v>355</v>
       </c>
       <c r="O58" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="P58" t="s">
         <v>356</v>
@@ -7469,7 +7472,7 @@
         <v>755</v>
       </c>
       <c r="C59" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D59" t="s">
         <v>359</v>
@@ -7515,7 +7518,7 @@
         <v>755</v>
       </c>
       <c r="C60" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D60" t="s">
         <v>362</v>
@@ -7524,7 +7527,7 @@
         <v>363</v>
       </c>
       <c r="F60" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="G60" t="s">
         <v>364</v>
@@ -7568,7 +7571,7 @@
         <v>772</v>
       </c>
       <c r="C61" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D61" t="s">
         <v>367</v>
@@ -7610,7 +7613,7 @@
       <c r="D62"/>
       <c r="E62"/>
       <c r="F62" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="G62" t="s">
         <v>370</v>
@@ -7654,7 +7657,7 @@
         <v>759</v>
       </c>
       <c r="C63" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D63" t="s">
         <v>374</v>
@@ -7663,7 +7666,7 @@
         <v>375</v>
       </c>
       <c r="F63" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="G63" t="s">
         <v>376</v>
@@ -7709,7 +7712,7 @@
       <c r="D64"/>
       <c r="E64"/>
       <c r="F64" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="G64" t="s">
         <v>379</v>
@@ -7753,7 +7756,7 @@
         <v>773</v>
       </c>
       <c r="C65" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D65" t="s">
         <v>383</v>
@@ -7764,7 +7767,7 @@
       <c r="G65"/>
       <c r="H65"/>
       <c r="I65" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="J65" t="s">
         <v>385</v>
@@ -7773,7 +7776,7 @@
         <v>386</v>
       </c>
       <c r="L65" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="M65" t="s">
         <v>387</v>
@@ -7782,7 +7785,7 @@
         <v>388</v>
       </c>
       <c r="O65" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="P65" t="s">
         <v>389</v>
@@ -7799,7 +7802,7 @@
         <v>759</v>
       </c>
       <c r="C66" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D66" t="s">
         <v>392</v>
@@ -7810,7 +7813,7 @@
       <c r="G66"/>
       <c r="H66"/>
       <c r="I66" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="J66" t="s">
         <v>394</v>
@@ -7819,7 +7822,7 @@
         <v>395</v>
       </c>
       <c r="L66" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="M66" t="s">
         <v>396</v>
@@ -7828,7 +7831,7 @@
         <v>397</v>
       </c>
       <c r="O66" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="P66" t="s">
         <v>398</v>
@@ -7845,7 +7848,7 @@
         <v>759</v>
       </c>
       <c r="C67" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D67" t="s">
         <v>401</v>
@@ -7856,7 +7859,7 @@
       <c r="G67"/>
       <c r="H67"/>
       <c r="I67" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="J67" t="s">
         <v>403</v>
@@ -7865,7 +7868,7 @@
         <v>404</v>
       </c>
       <c r="L67" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="M67" t="s">
         <v>405</v>
@@ -7874,7 +7877,7 @@
         <v>406</v>
       </c>
       <c r="O67" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="P67" t="s">
         <v>407</v>
@@ -7893,7 +7896,7 @@
       <c r="D68"/>
       <c r="E68"/>
       <c r="F68" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G68" t="s">
         <v>410</v>
@@ -7918,7 +7921,7 @@
       <c r="D69"/>
       <c r="E69"/>
       <c r="F69" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="G69" t="s">
         <v>413</v>
@@ -7962,7 +7965,7 @@
         <v>774</v>
       </c>
       <c r="C70" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D70" t="s">
         <v>416</v>
@@ -7973,7 +7976,7 @@
       <c r="G70"/>
       <c r="H70"/>
       <c r="I70" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="J70" t="s">
         <v>418</v>
@@ -7982,7 +7985,7 @@
         <v>419</v>
       </c>
       <c r="L70" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M70" t="s">
         <v>420</v>
@@ -7991,7 +7994,7 @@
         <v>421</v>
       </c>
       <c r="O70" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="P70" t="s">
         <v>422</v>
@@ -8008,7 +8011,7 @@
         <v>755</v>
       </c>
       <c r="C71" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D71" t="s">
         <v>425</v>
@@ -8033,7 +8036,7 @@
         <v>759</v>
       </c>
       <c r="C72" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D72" t="s">
         <v>428</v>
@@ -8058,7 +8061,7 @@
         <v>755</v>
       </c>
       <c r="C73" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D73" t="s">
         <v>431</v>
@@ -8083,7 +8086,7 @@
         <v>755</v>
       </c>
       <c r="C74" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D74" t="s">
         <v>434</v>
@@ -8108,7 +8111,7 @@
         <v>755</v>
       </c>
       <c r="C75" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D75"/>
       <c r="E75" t="s">
@@ -8117,7 +8120,7 @@
       <c r="G75"/>
       <c r="H75"/>
       <c r="I75" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="J75"/>
       <c r="K75" t="s">
@@ -8136,7 +8139,7 @@
         <v>775</v>
       </c>
       <c r="C76" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D76" t="s">
         <v>440</v>
@@ -8147,7 +8150,7 @@
       <c r="G76"/>
       <c r="H76"/>
       <c r="I76" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="J76" t="s">
         <v>442</v>
@@ -8156,7 +8159,7 @@
         <v>443</v>
       </c>
       <c r="L76" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="M76" t="s">
         <v>444</v>
@@ -8165,7 +8168,7 @@
         <v>445</v>
       </c>
       <c r="O76" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="P76" t="s">
         <v>446</v>
@@ -8182,7 +8185,7 @@
         <v>755</v>
       </c>
       <c r="C77" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D77"/>
       <c r="E77" t="s">
@@ -8191,7 +8194,7 @@
       <c r="G77"/>
       <c r="H77"/>
       <c r="I77" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="J77"/>
       <c r="K77" t="s">
@@ -8210,7 +8213,7 @@
         <v>755</v>
       </c>
       <c r="C78" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D78"/>
       <c r="E78" t="s">
@@ -8219,21 +8222,21 @@
       <c r="G78"/>
       <c r="H78"/>
       <c r="I78" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="J78"/>
       <c r="K78" t="s">
         <v>453</v>
       </c>
       <c r="L78" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="M78"/>
       <c r="N78" t="s">
         <v>454</v>
       </c>
       <c r="O78" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="P78" t="s">
         <v>455</v>
@@ -8250,7 +8253,7 @@
         <v>776</v>
       </c>
       <c r="C79" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D79" t="s">
         <v>458</v>
@@ -8261,21 +8264,21 @@
       <c r="G79"/>
       <c r="H79"/>
       <c r="I79" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="J79"/>
       <c r="K79" t="s">
         <v>453</v>
       </c>
       <c r="L79" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="M79"/>
       <c r="N79" t="s">
         <v>460</v>
       </c>
       <c r="O79" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="P79" t="s">
         <v>455</v>
@@ -8298,7 +8301,7 @@
       <c r="J80"/>
       <c r="K80"/>
       <c r="L80" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="M80" t="s">
         <v>463</v>
@@ -8317,7 +8320,7 @@
         <v>764</v>
       </c>
       <c r="C81" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D81" t="s">
         <v>167</v>
@@ -8328,7 +8331,7 @@
       <c r="G81"/>
       <c r="H81"/>
       <c r="I81" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="J81" t="s">
         <v>466</v>
@@ -8337,7 +8340,7 @@
         <v>467</v>
       </c>
       <c r="L81" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M81" t="s">
         <v>468</v>
@@ -8346,7 +8349,7 @@
         <v>469</v>
       </c>
       <c r="O81" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="P81" t="s">
         <v>470</v>
@@ -8363,7 +8366,7 @@
         <v>755</v>
       </c>
       <c r="C82" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D82" t="s">
         <v>473</v>
@@ -8388,7 +8391,7 @@
         <v>755</v>
       </c>
       <c r="C83" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D83" t="s">
         <v>476</v>
@@ -8413,7 +8416,7 @@
         <v>761</v>
       </c>
       <c r="C84" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D84" t="s">
         <v>479</v>
@@ -8426,7 +8429,7 @@
       <c r="J84"/>
       <c r="K84"/>
       <c r="L84" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M84" t="s">
         <v>481</v>
@@ -8445,7 +8448,7 @@
         <v>761</v>
       </c>
       <c r="C85" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D85" t="s">
         <v>484</v>
@@ -8458,7 +8461,7 @@
       <c r="J85"/>
       <c r="K85"/>
       <c r="L85" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="M85" t="s">
         <v>486</v>
@@ -8477,7 +8480,7 @@
         <v>755</v>
       </c>
       <c r="C86" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D86"/>
       <c r="E86" t="s">
@@ -8500,7 +8503,7 @@
         <v>755</v>
       </c>
       <c r="C87" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D87" t="s">
         <v>491</v>
@@ -8511,14 +8514,14 @@
       <c r="G87"/>
       <c r="H87"/>
       <c r="I87" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="J87"/>
       <c r="K87" t="s">
         <v>493</v>
       </c>
       <c r="L87" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M87"/>
       <c r="N87" t="s">
@@ -8535,7 +8538,7 @@
         <v>755</v>
       </c>
       <c r="C88" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D88" t="s">
         <v>495</v>
@@ -8546,7 +8549,7 @@
       <c r="G88"/>
       <c r="H88"/>
       <c r="I88" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="J88" t="s">
         <v>497</v>
@@ -8555,7 +8558,7 @@
         <v>498</v>
       </c>
       <c r="L88" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="M88" t="s">
         <v>499</v>
@@ -8564,7 +8567,7 @@
         <v>500</v>
       </c>
       <c r="O88" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="P88" t="s">
         <v>501</v>
@@ -8581,7 +8584,7 @@
         <v>759</v>
       </c>
       <c r="C89" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D89" t="s">
         <v>504</v>
@@ -8606,7 +8609,7 @@
         <v>769</v>
       </c>
       <c r="C90" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D90" t="s">
         <v>507</v>
@@ -8619,7 +8622,7 @@
       <c r="J90"/>
       <c r="K90"/>
       <c r="L90" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="M90" t="s">
         <v>509</v>
@@ -8628,7 +8631,7 @@
         <v>510</v>
       </c>
       <c r="O90" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="P90" t="s">
         <v>511</v>
@@ -8651,7 +8654,7 @@
       <c r="J91"/>
       <c r="K91"/>
       <c r="L91" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="M91" t="s">
         <v>514</v>
@@ -8660,7 +8663,7 @@
         <v>286</v>
       </c>
       <c r="O91" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="P91" t="s">
         <v>515</v>
@@ -8679,7 +8682,7 @@
       <c r="D92"/>
       <c r="E92"/>
       <c r="F92" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G92" t="s">
         <v>518</v>
@@ -8723,7 +8726,7 @@
         <v>755</v>
       </c>
       <c r="C93" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D93" t="s">
         <v>521</v>
@@ -8732,7 +8735,7 @@
         <v>522</v>
       </c>
       <c r="F93" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G93" t="s">
         <v>523</v>
@@ -8755,7 +8758,7 @@
         <v>755</v>
       </c>
       <c r="C94" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D94" t="s">
         <v>526</v>
@@ -8764,7 +8767,7 @@
         <v>522</v>
       </c>
       <c r="F94" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="G94" t="s">
         <v>527</v>
@@ -8787,7 +8790,7 @@
         <v>755</v>
       </c>
       <c r="C95" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D95" t="s">
         <v>530</v>
@@ -8796,7 +8799,7 @@
         <v>531</v>
       </c>
       <c r="F95" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="G95" t="s">
         <v>532</v>
@@ -8823,7 +8826,7 @@
       <c r="G96"/>
       <c r="H96"/>
       <c r="I96" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="J96" t="s">
         <v>535</v>
@@ -8832,7 +8835,7 @@
         <v>536</v>
       </c>
       <c r="L96" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="M96" t="s">
         <v>537</v>
@@ -8841,7 +8844,7 @@
         <v>538</v>
       </c>
       <c r="O96" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="P96" t="s">
         <v>539</v>
@@ -8862,7 +8865,7 @@
       <c r="G97"/>
       <c r="H97"/>
       <c r="I97" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="J97" t="s">
         <v>542</v>
@@ -8871,7 +8874,7 @@
         <v>543</v>
       </c>
       <c r="L97" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="M97" t="s">
         <v>544</v>
@@ -8894,7 +8897,7 @@
       <c r="G98"/>
       <c r="H98"/>
       <c r="I98" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="J98" t="s">
         <v>542</v>
@@ -8903,7 +8906,7 @@
         <v>543</v>
       </c>
       <c r="L98" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="M98" t="s">
         <v>547</v>
@@ -8922,7 +8925,7 @@
         <v>755</v>
       </c>
       <c r="C99" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D99" t="s">
         <v>550</v>
@@ -8947,7 +8950,7 @@
         <v>755</v>
       </c>
       <c r="C100" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D100" t="s">
         <v>553</v>
@@ -8972,7 +8975,7 @@
         <v>755</v>
       </c>
       <c r="C101" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D101" t="s">
         <v>556</v>
@@ -8981,7 +8984,7 @@
         <v>557</v>
       </c>
       <c r="F101" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="G101" t="s">
         <v>558</v>
@@ -9001,10 +9004,10 @@
         <v>560</v>
       </c>
       <c r="B102" t="s">
-        <v>18</v>
+        <v>758</v>
       </c>
       <c r="C102" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D102" t="s">
         <v>561</v>
@@ -9015,7 +9018,7 @@
       <c r="G102"/>
       <c r="H102"/>
       <c r="I102" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="J102" t="s">
         <v>563</v>
@@ -9024,7 +9027,7 @@
         <v>564</v>
       </c>
       <c r="L102" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="M102" t="s">
         <v>565</v>
@@ -9033,7 +9036,7 @@
         <v>566</v>
       </c>
       <c r="O102" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="P102" t="s">
         <v>567</v>
@@ -9050,7 +9053,7 @@
         <v>755</v>
       </c>
       <c r="C103" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D103" t="s">
         <v>570</v>
@@ -9075,7 +9078,7 @@
         <v>775</v>
       </c>
       <c r="C104" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D104" t="s">
         <v>573</v>
@@ -9100,7 +9103,7 @@
         <v>778</v>
       </c>
       <c r="C105" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D105" t="s">
         <v>576</v>
@@ -9149,7 +9152,7 @@
       <c r="J107"/>
       <c r="K107"/>
       <c r="L107" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="M107" t="s">
         <v>580</v>
@@ -9168,7 +9171,7 @@
         <v>780</v>
       </c>
       <c r="C108" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D108" t="s">
         <v>583</v>
@@ -9179,7 +9182,7 @@
       <c r="G108"/>
       <c r="H108"/>
       <c r="I108" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="J108" t="s">
         <v>585</v>
@@ -9188,7 +9191,7 @@
         <v>586</v>
       </c>
       <c r="L108" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="M108" t="s">
         <v>587</v>
@@ -9197,7 +9200,7 @@
         <v>588</v>
       </c>
       <c r="O108" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="P108" t="s">
         <v>589</v>
@@ -9214,7 +9217,7 @@
         <v>781</v>
       </c>
       <c r="C109" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D109" t="s">
         <v>592</v>
@@ -9225,7 +9228,7 @@
       <c r="G109"/>
       <c r="H109"/>
       <c r="I109" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="J109" t="s">
         <v>594</v>
@@ -9234,7 +9237,7 @@
         <v>595</v>
       </c>
       <c r="L109" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="M109" t="s">
         <v>596</v>
@@ -9243,7 +9246,7 @@
         <v>597</v>
       </c>
       <c r="O109" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="P109" t="s">
         <v>598</v>
@@ -9260,7 +9263,7 @@
         <v>757</v>
       </c>
       <c r="C110" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D110" t="s">
         <v>601</v>
@@ -9271,7 +9274,7 @@
       <c r="G110"/>
       <c r="H110"/>
       <c r="I110" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="J110" t="s">
         <v>603</v>
@@ -9280,7 +9283,7 @@
         <v>604</v>
       </c>
       <c r="L110" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="M110" t="s">
         <v>514</v>
@@ -9289,7 +9292,7 @@
         <v>286</v>
       </c>
       <c r="O110" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="P110" t="s">
         <v>605</v>
@@ -9306,7 +9309,7 @@
         <v>780</v>
       </c>
       <c r="C111" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D111" t="s">
         <v>608</v>
@@ -9317,7 +9320,7 @@
       <c r="G111"/>
       <c r="H111"/>
       <c r="I111" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="J111" t="s">
         <v>610</v>
@@ -9326,7 +9329,7 @@
         <v>611</v>
       </c>
       <c r="L111" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="M111" t="s">
         <v>612</v>
@@ -9335,7 +9338,7 @@
         <v>613</v>
       </c>
       <c r="O111" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="P111" t="s">
         <v>614</v>
@@ -9352,7 +9355,7 @@
         <v>782</v>
       </c>
       <c r="C112" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D112" t="s">
         <v>617</v>
@@ -9363,7 +9366,7 @@
       <c r="G112"/>
       <c r="H112"/>
       <c r="I112" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="J112" t="s">
         <v>619</v>
@@ -9372,7 +9375,7 @@
         <v>620</v>
       </c>
       <c r="L112" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="M112" t="s">
         <v>621</v>
@@ -9381,7 +9384,7 @@
         <v>622</v>
       </c>
       <c r="O112" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="P112" t="s">
         <v>623</v>
@@ -9395,14 +9398,14 @@
         <v>625</v>
       </c>
       <c r="B113" t="s">
-        <v>758</v>
+        <v>783</v>
       </c>
       <c r="D113"/>
       <c r="E113"/>
       <c r="G113"/>
       <c r="H113"/>
       <c r="I113" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="J113" t="s">
         <v>626</v>
@@ -9411,7 +9414,7 @@
         <v>627</v>
       </c>
       <c r="L113" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="M113" t="s">
         <v>628</v>
@@ -9420,7 +9423,7 @@
         <v>629</v>
       </c>
       <c r="O113" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="P113" t="s">
         <v>630</v>
@@ -9434,14 +9437,14 @@
         <v>632</v>
       </c>
       <c r="B114" t="s">
-        <v>758</v>
+        <v>783</v>
       </c>
       <c r="D114"/>
       <c r="E114"/>
       <c r="G114"/>
       <c r="H114"/>
       <c r="I114" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="J114" t="s">
         <v>633</v>
@@ -9450,7 +9453,7 @@
         <v>634</v>
       </c>
       <c r="L114" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="M114" t="s">
         <v>635</v>
@@ -9459,7 +9462,7 @@
         <v>636</v>
       </c>
       <c r="O114" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="P114" t="s">
         <v>637</v>
@@ -9476,7 +9479,7 @@
         <v>782</v>
       </c>
       <c r="C115" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D115" t="s">
         <v>640</v>
@@ -9487,7 +9490,7 @@
       <c r="G115"/>
       <c r="H115"/>
       <c r="I115" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J115" t="s">
         <v>642</v>
@@ -9496,7 +9499,7 @@
         <v>643</v>
       </c>
       <c r="L115" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M115" t="s">
         <v>644</v>
@@ -9505,7 +9508,7 @@
         <v>645</v>
       </c>
       <c r="O115" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="P115" t="s">
         <v>646</v>
@@ -9522,7 +9525,7 @@
         <v>764</v>
       </c>
       <c r="C116" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D116" t="s">
         <v>649</v>
@@ -9533,7 +9536,7 @@
       <c r="G116"/>
       <c r="H116"/>
       <c r="I116" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="J116" t="s">
         <v>651</v>
@@ -9542,7 +9545,7 @@
         <v>652</v>
       </c>
       <c r="L116" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="M116" t="s">
         <v>653</v>
@@ -9551,7 +9554,7 @@
         <v>654</v>
       </c>
       <c r="O116" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="P116" t="s">
         <v>646</v>
@@ -9568,7 +9571,7 @@
         <v>770</v>
       </c>
       <c r="C117" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D117" t="s">
         <v>656</v>
@@ -9579,7 +9582,7 @@
       <c r="G117"/>
       <c r="H117"/>
       <c r="I117" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="J117" t="s">
         <v>658</v>
@@ -9588,7 +9591,7 @@
         <v>659</v>
       </c>
       <c r="L117" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="M117" t="s">
         <v>660</v>
@@ -9597,7 +9600,7 @@
         <v>661</v>
       </c>
       <c r="O117" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="P117" t="s">
         <v>662</v>
@@ -9611,10 +9614,10 @@
         <v>664</v>
       </c>
       <c r="B118" t="s">
-        <v>18</v>
+        <v>758</v>
       </c>
       <c r="C118" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D118" t="s">
         <v>665</v>
@@ -9625,7 +9628,7 @@
       <c r="G118"/>
       <c r="H118"/>
       <c r="I118" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="J118" t="s">
         <v>667</v>
@@ -9634,7 +9637,7 @@
         <v>668</v>
       </c>
       <c r="L118" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M118" t="s">
         <v>669</v>
@@ -9643,7 +9646,7 @@
         <v>670</v>
       </c>
       <c r="O118" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="P118" t="s">
         <v>671</v>
@@ -9657,10 +9660,10 @@
         <v>673</v>
       </c>
       <c r="B119" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C119" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D119" t="s">
         <v>674</v>
@@ -9671,7 +9674,7 @@
       <c r="G119"/>
       <c r="H119"/>
       <c r="I119" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="J119" t="s">
         <v>676</v>
@@ -9680,7 +9683,7 @@
         <v>677</v>
       </c>
       <c r="L119" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="M119" t="s">
         <v>678</v>
@@ -9689,7 +9692,7 @@
         <v>679</v>
       </c>
       <c r="O119" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="P119" t="s">
         <v>680</v>
@@ -9703,7 +9706,7 @@
         <v>682</v>
       </c>
       <c r="B120" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C120" t="s">
         <v>683</v>
@@ -9728,7 +9731,7 @@
         <v>684</v>
       </c>
       <c r="B121" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C121" t="s">
         <v>683</v>
@@ -9742,7 +9745,7 @@
       <c r="G121"/>
       <c r="H121"/>
       <c r="I121" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="J121" t="s">
         <v>685</v>
@@ -9751,7 +9754,7 @@
         <v>686</v>
       </c>
       <c r="L121" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="M121" t="s">
         <v>687</v>
@@ -9760,7 +9763,7 @@
         <v>688</v>
       </c>
       <c r="O121" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="P121" t="s">
         <v>689</v>
@@ -9774,7 +9777,7 @@
         <v>691</v>
       </c>
       <c r="B122" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C122" t="s">
         <v>683</v>
@@ -9788,7 +9791,7 @@
       <c r="G122"/>
       <c r="H122"/>
       <c r="I122" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="J122" t="s">
         <v>692</v>
@@ -9797,7 +9800,7 @@
         <v>693</v>
       </c>
       <c r="L122" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="M122" t="s">
         <v>694</v>
@@ -9806,7 +9809,7 @@
         <v>695</v>
       </c>
       <c r="O122" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="P122" t="s">
         <v>696</v>
@@ -9823,7 +9826,7 @@
         <v>757</v>
       </c>
       <c r="C123" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D123" t="s">
         <v>699</v>
@@ -9836,7 +9839,7 @@
       <c r="J123"/>
       <c r="K123"/>
       <c r="L123" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="M123" t="s">
         <v>701</v>
@@ -9845,7 +9848,7 @@
         <v>702</v>
       </c>
       <c r="O123" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="P123" t="s">
         <v>703</v>
@@ -9862,7 +9865,7 @@
         <v>757</v>
       </c>
       <c r="C124" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D124" t="s">
         <v>706</v>
@@ -9875,7 +9878,7 @@
       <c r="J124"/>
       <c r="K124"/>
       <c r="L124" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="M124" t="s">
         <v>708</v>
@@ -9891,10 +9894,10 @@
         <v>710</v>
       </c>
       <c r="B125" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C125" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D125" t="s">
         <v>711</v>
@@ -9905,7 +9908,7 @@
       <c r="G125"/>
       <c r="H125"/>
       <c r="I125" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="J125" t="s">
         <v>713</v>
@@ -9914,7 +9917,7 @@
         <v>714</v>
       </c>
       <c r="L125" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="M125" t="s">
         <v>715</v>
@@ -9923,7 +9926,7 @@
         <v>716</v>
       </c>
       <c r="O125" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="P125" t="s">
         <v>717</v>
@@ -9940,7 +9943,7 @@
         <v>757</v>
       </c>
       <c r="C126" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D126" t="s">
         <v>720</v>
@@ -9951,7 +9954,7 @@
       <c r="G126"/>
       <c r="H126"/>
       <c r="I126" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="J126" t="s">
         <v>722</v>
@@ -9960,7 +9963,7 @@
         <v>723</v>
       </c>
       <c r="L126" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="M126" t="s">
         <v>724</v>
@@ -9969,7 +9972,7 @@
         <v>725</v>
       </c>
       <c r="O126" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="P126" t="s">
         <v>726</v>
@@ -9983,10 +9986,10 @@
         <v>728</v>
       </c>
       <c r="B127" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C127" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D127" t="s">
         <v>729</v>
@@ -9997,7 +10000,7 @@
       <c r="G127"/>
       <c r="H127"/>
       <c r="I127" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="J127" t="s">
         <v>731</v>
@@ -10006,7 +10009,7 @@
         <v>732</v>
       </c>
       <c r="L127" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="M127" t="s">
         <v>733</v>
@@ -10015,7 +10018,7 @@
         <v>734</v>
       </c>
       <c r="O127" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="P127" t="s">
         <v>735</v>
@@ -10029,10 +10032,10 @@
         <v>737</v>
       </c>
       <c r="B128" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C128" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D128" t="s">
         <v>738</v>
@@ -10043,7 +10046,7 @@
       <c r="G128"/>
       <c r="H128"/>
       <c r="I128" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="J128" t="s">
         <v>740</v>
@@ -10052,7 +10055,7 @@
         <v>741</v>
       </c>
       <c r="L128" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="M128" t="s">
         <v>742</v>
@@ -10061,7 +10064,7 @@
         <v>743</v>
       </c>
       <c r="O128" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="P128" t="s">
         <v>744</v>
@@ -10075,10 +10078,10 @@
         <v>746</v>
       </c>
       <c r="B129" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C129" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D129" t="s">
         <v>747</v>
@@ -10107,7 +10110,7 @@
       <c r="G130"/>
       <c r="H130"/>
       <c r="I130" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="J130" t="s">
         <v>750</v>
@@ -10116,7 +10119,7 @@
         <v>751</v>
       </c>
       <c r="L130" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="M130" t="s">
         <v>752</v>
@@ -10125,7 +10128,7 @@
         <v>460</v>
       </c>
       <c r="O130" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="P130" t="s">
         <v>753</v>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">artist</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.281</t>
+    <t xml:space="preserve">EA 23.282 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">"You senseless bastard!"

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">artist</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282 Patch 2</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">"You senseless bastard!"

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="1103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="1103">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">artist</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">"You senseless bastard!"
@@ -137,7 +137,7 @@
   <si>
     <t xml:space="preserve"> *パタパタ*
  * ばさっばさっ*
-*ハタハタ*</t>
+ *ハタハタ*</t>
   </si>
   <si>
     <t xml:space="preserve">"Aaah!"</t>
@@ -430,7 +430,7 @@
     <t xml:space="preserve">「うみみゃ」
 「みゅー」
 「みゃ」
-*ごろごろ*</t>
+ *ごろごろ*</t>
   </si>
   <si>
     <t xml:space="preserve">「フシューッ」
@@ -2538,7 +2538,7 @@
     <t xml:space="preserve"> *ドスン*
 リトルシスター「見て#bigdaddy、天使がいるわ」
 リトルシスター「急いで#bigdaddy、空で天使が踊っているの！」
-*ドン*</t>
+ *ドン*</t>
   </si>
   <si>
     <t xml:space="preserve">Little Sister: "Kill! Kill!"
@@ -2998,7 +2998,7 @@
   <si>
     <t xml:space="preserve">「あんな極上の女はそうはいねえ」
 「俺の手に掛かれば、どんな女もイチコロよ」
-*レロレロレロ*
+ *レロレロレロ*
 「まったく罪な男に生まれちまったもんだ」</t>
   </si>
   <si>
@@ -5286,7 +5286,7 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>758</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>790</v>
@@ -5625,7 +5625,7 @@
         <v>95</v>
       </c>
       <c r="B14" t="s">
-        <v>758</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>798</v>
@@ -9004,7 +9004,7 @@
         <v>560</v>
       </c>
       <c r="B102" t="s">
-        <v>758</v>
+        <v>18</v>
       </c>
       <c r="C102" t="s">
         <v>857</v>
@@ -9614,7 +9614,7 @@
         <v>664</v>
       </c>
       <c r="B118" t="s">
-        <v>758</v>
+        <v>18</v>
       </c>
       <c r="C118" t="s">
         <v>869</v>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="1129">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -2553,6 +2553,44 @@
   </si>
   <si>
     <t xml:space="preserve">「愚か者め」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sad_creature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「여줘…」
+「죽여줘…」
+「또…」
+「늘어나…」
+「많이…」
+「에드…」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"please..."
+"kill me..."
+"again..."
+"growing..."
+"so many..."
+”Ed...ward..."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「ｼﾃ…」
+「ｺﾛｼﾃ…」
+「ﾏﾀ…」
+「ﾌｴﾙ…」
+「ﾀｸｻﾝ…」
+「ｴﾄﾞ…」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「여줘…」
+「죽여줘…」
+「아직…」
+「늘어나…」
+「많이…」
+「에드…」</t>
   </si>
   <si>
     <t xml:space="preserve">sailor</t>
@@ -5369,7 +5407,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q132"/>
+  <dimension ref="A1:Q133"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="1" style="0" width="16.15"/>
@@ -7587,74 +7625,74 @@
         <v>540</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
         <v>541</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>18</v>
+        <v>542</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="G61" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="I61" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="J61" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="K61" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="L61" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="M61" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="N61" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="O61" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="P61" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q61" s="0" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H61" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q61" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="G62" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="I62" s="0" t="s">
         <v>241</v>
@@ -7684,835 +7722,859 @@
         <v>241</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="141" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
+        <v>551</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="D63" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="E63" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="F63" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="G63" s="2" t="s">
         <v>556</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>557</v>
       </c>
       <c r="I63" s="0" t="s">
         <v>241</v>
       </c>
+      <c r="J63" s="0" t="s">
+        <v>241</v>
+      </c>
       <c r="K63" s="0" t="s">
         <v>241</v>
       </c>
       <c r="L63" s="0" t="s">
         <v>241</v>
       </c>
+      <c r="M63" s="0" t="s">
+        <v>241</v>
+      </c>
       <c r="N63" s="0" t="s">
         <v>241</v>
       </c>
       <c r="O63" s="0" t="s">
         <v>241</v>
       </c>
+      <c r="P63" s="0" t="s">
+        <v>241</v>
+      </c>
       <c r="Q63" s="0" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="141" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B64" s="0" t="s">
+        <v>559</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="I64" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="K64" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="L64" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="N64" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="O64" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q64" s="0" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="s">
+        <v>563</v>
+      </c>
+      <c r="B65" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="I64" s="0" t="s">
-        <v>561</v>
-      </c>
-      <c r="J64" s="0" t="s">
-        <v>561</v>
-      </c>
-      <c r="K64" s="0" t="s">
-        <v>561</v>
-      </c>
-      <c r="L64" s="0" t="s">
-        <v>561</v>
-      </c>
-      <c r="M64" s="0" t="s">
-        <v>561</v>
-      </c>
-      <c r="N64" s="0" t="s">
-        <v>561</v>
-      </c>
-      <c r="O64" s="0" t="s">
-        <v>561</v>
-      </c>
-      <c r="P64" s="0" t="s">
-        <v>561</v>
-      </c>
-      <c r="Q64" s="0" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
-        <v>562</v>
-      </c>
-      <c r="B65" s="0" t="s">
+      <c r="F65" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="I65" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="J65" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="K65" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="L65" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="M65" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="N65" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="O65" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="P65" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="Q65" s="0" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="s">
+        <v>568</v>
+      </c>
+      <c r="B66" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="I65" s="0" t="s">
+      <c r="C66" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="I66" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="J65" s="0" t="s">
+      <c r="J66" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="K65" s="0" t="s">
+      <c r="K66" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="L65" s="0" t="s">
+      <c r="L66" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="M65" s="0" t="s">
+      <c r="M66" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="N65" s="0" t="s">
+      <c r="N66" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="O65" s="0" t="s">
+      <c r="O66" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="P65" s="0" t="s">
+      <c r="P66" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="Q65" s="0" t="s">
+      <c r="Q66" s="0" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
-        <v>569</v>
-      </c>
-      <c r="B66" s="0" t="s">
+    <row r="67" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="s">
+        <v>575</v>
+      </c>
+      <c r="B67" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="I66" s="0" t="s">
-        <v>573</v>
-      </c>
-      <c r="J66" s="0" t="s">
-        <v>573</v>
-      </c>
-      <c r="K66" s="0" t="s">
-        <v>573</v>
-      </c>
-      <c r="L66" s="0" t="s">
-        <v>573</v>
-      </c>
-      <c r="M66" s="0" t="s">
-        <v>573</v>
-      </c>
-      <c r="N66" s="0" t="s">
-        <v>573</v>
-      </c>
-      <c r="O66" s="0" t="s">
-        <v>573</v>
-      </c>
-      <c r="P66" s="0" t="s">
-        <v>573</v>
-      </c>
-      <c r="Q66" s="0" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
-        <v>574</v>
-      </c>
-      <c r="B67" s="0" t="s">
-        <v>575</v>
-      </c>
-      <c r="C67" s="2" t="s">
+      <c r="F67" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="G67" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="H67" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="I67" s="2" t="s">
+      <c r="I67" s="0" t="s">
         <v>579</v>
       </c>
-      <c r="J67" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="L67" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="M67" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="N67" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="O67" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="P67" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="Q67" s="2" t="s">
-        <v>587</v>
+      <c r="J67" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="K67" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="L67" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="M67" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="N67" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="O67" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="P67" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="Q67" s="0" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
+        <v>580</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="L68" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="B68" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="C68" s="2" t="s">
+      <c r="M68" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="N68" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="O68" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="I68" s="2" t="s">
+      <c r="P68" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="J68" s="2" t="s">
+      <c r="Q68" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="K68" s="2" t="s">
+    </row>
+    <row r="69" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="s">
         <v>594</v>
-      </c>
-      <c r="L68" s="0" t="s">
-        <v>595</v>
-      </c>
-      <c r="M68" s="0" t="s">
-        <v>596</v>
-      </c>
-      <c r="N68" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="O68" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="P68" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="Q68" s="2" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
-        <v>601</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>100</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="L69" s="0" t="s">
+        <v>601</v>
+      </c>
+      <c r="M69" s="0" t="s">
         <v>602</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="N69" s="0" t="s">
         <v>603</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="O69" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="I69" s="2" t="s">
+      <c r="P69" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="J69" s="2" t="s">
+      <c r="Q69" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="K69" s="2" t="s">
+    </row>
+    <row r="70" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="s">
         <v>607</v>
       </c>
-      <c r="L69" s="0" t="s">
+      <c r="B70" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="M69" s="0" t="s">
+      <c r="D70" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="N69" s="0" t="s">
+      <c r="E70" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="O69" s="0" t="s">
+      <c r="I70" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="P69" s="0" t="s">
+      <c r="J70" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="Q69" s="0" t="s">
+      <c r="K70" s="2" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="70" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="L70" s="0" t="s">
         <v>614</v>
       </c>
-      <c r="B70" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="F70" s="2" t="s">
+      <c r="M70" s="0" t="s">
         <v>615</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="N70" s="0" t="s">
         <v>616</v>
       </c>
-      <c r="H70" s="2" t="s">
+      <c r="O70" s="0" t="s">
         <v>617</v>
+      </c>
+      <c r="P70" s="0" t="s">
+        <v>618</v>
+      </c>
+      <c r="Q70" s="0" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>18</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="I71" s="0" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="s">
+        <v>624</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="I72" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="J71" s="0" t="s">
+      <c r="J72" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="K71" s="0" t="s">
+      <c r="K72" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="L71" s="0" t="s">
+      <c r="L72" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="M71" s="0" t="s">
+      <c r="M72" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="N71" s="0" t="s">
+      <c r="N72" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="O71" s="0" t="s">
+      <c r="O72" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="P71" s="0" t="s">
+      <c r="P72" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="Q71" s="0" t="s">
+      <c r="Q72" s="0" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
-        <v>622</v>
-      </c>
-      <c r="B72" s="0" t="s">
-        <v>623</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="J72" s="2" t="s">
+    <row r="73" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
         <v>628</v>
       </c>
-      <c r="K72" s="2" t="s">
+      <c r="B73" s="0" t="s">
         <v>629</v>
       </c>
-      <c r="L72" s="0" t="s">
+      <c r="C73" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="M72" s="0" t="s">
+      <c r="D73" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="N72" s="0" t="s">
+      <c r="E73" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="O72" s="0" t="s">
+      <c r="I73" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="P72" s="0" t="s">
+      <c r="J73" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="Q72" s="0" t="s">
+      <c r="K73" s="2" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="L73" s="0" t="s">
         <v>636</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="M73" s="0" t="s">
+        <v>637</v>
+      </c>
+      <c r="N73" s="0" t="s">
+        <v>638</v>
+      </c>
+      <c r="O73" s="0" t="s">
+        <v>639</v>
+      </c>
+      <c r="P73" s="0" t="s">
+        <v>640</v>
+      </c>
+      <c r="Q73" s="0" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="s">
+        <v>642</v>
+      </c>
+      <c r="B74" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
-        <v>640</v>
-      </c>
-      <c r="B74" s="0" t="s">
+      <c r="C74" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="s">
+        <v>646</v>
+      </c>
+      <c r="B75" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
-        <v>644</v>
-      </c>
-      <c r="B75" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="C75" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>656</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="I77" s="0" t="s">
-        <v>655</v>
-      </c>
-      <c r="K77" s="0" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>658</v>
+        <v>18</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="E78" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="I78" s="0" t="s">
         <v>661</v>
       </c>
-      <c r="I78" s="0" t="s">
+      <c r="K78" s="0" t="s">
         <v>662</v>
       </c>
-      <c r="J78" s="0" t="s">
+    </row>
+    <row r="79" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0" t="s">
         <v>663</v>
       </c>
-      <c r="K78" s="0" t="s">
+      <c r="B79" s="0" t="s">
         <v>664</v>
       </c>
-      <c r="L78" s="0" t="s">
+      <c r="C79" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="M78" s="0" t="s">
+      <c r="D79" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="N78" s="0" t="s">
+      <c r="E79" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="O78" s="0" t="s">
+      <c r="I79" s="0" t="s">
         <v>668</v>
       </c>
-      <c r="P78" s="0" t="s">
+      <c r="J79" s="0" t="s">
         <v>669</v>
       </c>
-      <c r="Q78" s="0" t="s">
+      <c r="K79" s="0" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="79" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="L79" s="0" t="s">
         <v>671</v>
       </c>
-      <c r="B79" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C79" s="2" t="s">
+      <c r="M79" s="0" t="s">
         <v>672</v>
       </c>
-      <c r="E79" s="2" t="s">
+      <c r="N79" s="0" t="s">
         <v>673</v>
       </c>
-      <c r="I79" s="0" t="s">
+      <c r="O79" s="0" t="s">
         <v>674</v>
       </c>
-      <c r="K79" s="0" t="s">
+      <c r="P79" s="0" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q79" s="0" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="K80" s="0" t="s">
-        <v>680</v>
-      </c>
-      <c r="L80" s="0" t="s">
         <v>681</v>
       </c>
-      <c r="N80" s="0" t="s">
+    </row>
+    <row r="81" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0" t="s">
         <v>682</v>
       </c>
-      <c r="O80" s="0" t="s">
+      <c r="B81" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="P80" s="0" t="s">
+      <c r="E81" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="Q80" s="0" t="s">
+      <c r="I81" s="0" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="K81" s="0" t="s">
         <v>686</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="L81" s="0" t="s">
         <v>687</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="N81" s="0" t="s">
         <v>688</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="O81" s="0" t="s">
         <v>689</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="P81" s="0" t="s">
         <v>690</v>
       </c>
-      <c r="I81" s="0" t="s">
+      <c r="Q81" s="0" t="s">
         <v>691</v>
       </c>
-      <c r="K81" s="0" t="s">
-        <v>680</v>
-      </c>
-      <c r="L81" s="0" t="s">
+    </row>
+    <row r="82" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="s">
         <v>692</v>
       </c>
-      <c r="N81" s="0" t="s">
+      <c r="B82" s="0" t="s">
         <v>693</v>
       </c>
-      <c r="O81" s="2" t="s">
+      <c r="C82" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="P81" s="0" t="s">
-        <v>684</v>
-      </c>
-      <c r="Q81" s="2" t="s">
+      <c r="D82" s="2" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="E82" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="B82" s="0" t="s">
-        <v>18</v>
+      <c r="I82" s="0" t="s">
+        <v>697</v>
+      </c>
+      <c r="K82" s="0" t="s">
+        <v>686</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>697</v>
-      </c>
-      <c r="M82" s="0" t="s">
         <v>698</v>
       </c>
       <c r="N82" s="0" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="83" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O82" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="P82" s="0" t="s">
+        <v>690</v>
+      </c>
+      <c r="Q82" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B83" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="L83" s="0" t="s">
+        <v>703</v>
+      </c>
+      <c r="M83" s="0" t="s">
+        <v>704</v>
+      </c>
+      <c r="N83" s="0" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="s">
+        <v>706</v>
+      </c>
+      <c r="B84" s="0" t="s">
         <v>243</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C84" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D84" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="E84" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="I83" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="J83" s="0" t="s">
-        <v>702</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="L83" s="0" t="s">
-        <v>704</v>
-      </c>
-      <c r="M83" s="0" t="s">
-        <v>705</v>
-      </c>
-      <c r="N83" s="0" t="s">
-        <v>706</v>
-      </c>
-      <c r="O83" s="0" t="s">
+      <c r="I84" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="P83" s="0" t="s">
+      <c r="J84" s="0" t="s">
         <v>708</v>
       </c>
-      <c r="Q83" s="0" t="s">
+      <c r="K84" s="2" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="L84" s="0" t="s">
         <v>710</v>
       </c>
-      <c r="B84" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C84" s="0" t="s">
+      <c r="M84" s="0" t="s">
         <v>711</v>
       </c>
-      <c r="D84" s="0" t="s">
+      <c r="N84" s="0" t="s">
         <v>712</v>
       </c>
-      <c r="E84" s="0" t="s">
+      <c r="O84" s="0" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="85" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P84" s="0" t="s">
+        <v>714</v>
+      </c>
+      <c r="Q84" s="0" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B85" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="E85" s="2" t="s">
+      <c r="C85" s="0" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D85" s="0" t="s">
+        <v>718</v>
+      </c>
+      <c r="E85" s="0" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="L86" s="0" t="s">
-        <v>722</v>
-      </c>
-      <c r="M86" s="0" t="s">
         <v>723</v>
       </c>
-      <c r="N86" s="0" t="s">
+    </row>
+    <row r="87" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="s">
         <v>724</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
-        <v>725</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>146</v>
       </c>
-      <c r="C87" s="0" t="s">
+      <c r="C87" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="D87" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="D87" s="0" t="s">
+      <c r="E87" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="E87" s="0" t="s">
+      <c r="L87" s="0" t="s">
         <v>728</v>
       </c>
-      <c r="L87" s="0" t="s">
+      <c r="M87" s="0" t="s">
         <v>729</v>
       </c>
-      <c r="M87" s="0" t="s">
+      <c r="N87" s="0" t="s">
         <v>730</v>
       </c>
-      <c r="N87" s="0" t="s">
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="88" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="B88" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="C88" s="0" t="s">
         <v>732</v>
       </c>
-      <c r="B88" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C88" s="2" t="s">
+      <c r="D88" s="0" t="s">
         <v>733</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="E88" s="0" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="89" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L88" s="0" t="s">
+        <v>735</v>
+      </c>
+      <c r="M88" s="0" t="s">
+        <v>736</v>
+      </c>
+      <c r="N88" s="0" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B89" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="K89" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="L89" s="0" t="s">
-        <v>425</v>
-      </c>
-      <c r="N89" s="0" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="90" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
         <v>741</v>
       </c>
@@ -8531,1400 +8593,1429 @@
       <c r="I90" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="J90" s="2" t="s">
+      <c r="K90" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="K90" s="2" t="s">
+      <c r="L90" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="N90" s="0" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="0" t="s">
         <v>747</v>
       </c>
-      <c r="L90" s="0" t="s">
+      <c r="B91" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="M90" s="0" t="s">
+      <c r="D91" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="N90" s="0" t="s">
+      <c r="E91" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="O90" s="0" t="s">
+      <c r="I91" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="P90" s="0" t="s">
+      <c r="J91" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="Q90" s="0" t="s">
+      <c r="K91" s="2" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="91" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="L91" s="0" t="s">
         <v>754</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="M91" s="0" t="s">
+        <v>755</v>
+      </c>
+      <c r="N91" s="0" t="s">
+        <v>756</v>
+      </c>
+      <c r="O91" s="0" t="s">
+        <v>757</v>
+      </c>
+      <c r="P91" s="0" t="s">
+        <v>758</v>
+      </c>
+      <c r="Q91" s="0" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="0" t="s">
+        <v>760</v>
+      </c>
+      <c r="B92" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="B92" s="0" t="s">
+      <c r="C92" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0" t="s">
+        <v>764</v>
+      </c>
+      <c r="B93" s="0" t="s">
         <v>358</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>760</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="L92" s="0" t="s">
-        <v>762</v>
-      </c>
-      <c r="M92" s="0" t="s">
-        <v>763</v>
-      </c>
-      <c r="N92" s="0" t="s">
-        <v>764</v>
-      </c>
-      <c r="O92" s="0" t="s">
+      <c r="C93" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="P92" s="0" t="s">
+      <c r="D93" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="Q92" s="0" t="s">
+      <c r="E93" s="2" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="93" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="L93" s="0" t="s">
         <v>768</v>
       </c>
-      <c r="B93" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L93" s="2" t="s">
+      <c r="M93" s="0" t="s">
         <v>769</v>
       </c>
-      <c r="M93" s="2" t="s">
+      <c r="N93" s="0" t="s">
         <v>770</v>
       </c>
-      <c r="N93" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="O93" s="2" t="s">
+      <c r="O93" s="0" t="s">
         <v>771</v>
       </c>
-      <c r="P93" s="2" t="s">
+      <c r="P93" s="0" t="s">
         <v>772</v>
       </c>
-      <c r="Q93" s="2" t="s">
+      <c r="Q93" s="0" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
         <v>774</v>
       </c>
       <c r="B94" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="F94" s="2" t="s">
+      <c r="L94" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="G94" s="2" t="s">
+      <c r="M94" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="H94" s="2" t="s">
+      <c r="N94" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="O94" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="I94" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="J94" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="K94" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="L94" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="M94" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="N94" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="O94" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="P94" s="0" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q94" s="0" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P94" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="Q94" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B95" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C95" s="0" t="s">
-        <v>779</v>
-      </c>
-      <c r="D95" s="0" t="s">
-        <v>780</v>
-      </c>
-      <c r="E95" s="0" t="s">
+      <c r="F95" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="F95" s="0" t="s">
+      <c r="G95" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="G95" s="0" t="s">
+      <c r="H95" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="H95" s="0" t="s">
-        <v>784</v>
+      <c r="I95" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="J95" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="K95" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="L95" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="M95" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="N95" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="O95" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="P95" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q95" s="0" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B96" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="D96" s="0" t="s">
         <v>786</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B97" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="D97" s="0" t="s">
         <v>792</v>
       </c>
       <c r="E97" s="0" t="s">
+        <v>787</v>
+      </c>
+      <c r="F97" s="0" t="s">
         <v>793</v>
       </c>
-      <c r="F97" s="0" t="s">
+      <c r="G97" s="0" t="s">
         <v>794</v>
       </c>
-      <c r="G97" s="0" t="s">
+      <c r="H97" s="0" t="s">
         <v>795</v>
-      </c>
-      <c r="H97" s="0" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
+        <v>796</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98" s="0" t="s">
         <v>797</v>
       </c>
-      <c r="B98" s="0" t="s">
+      <c r="D98" s="0" t="s">
         <v>798</v>
       </c>
-      <c r="I98" s="0" t="s">
+      <c r="E98" s="0" t="s">
         <v>799</v>
       </c>
-      <c r="J98" s="0" t="s">
+      <c r="F98" s="0" t="s">
         <v>800</v>
       </c>
-      <c r="K98" s="0" t="s">
+      <c r="G98" s="0" t="s">
         <v>801</v>
       </c>
-      <c r="L98" s="0" t="s">
+      <c r="H98" s="0" t="s">
         <v>802</v>
-      </c>
-      <c r="M98" s="0" t="s">
-        <v>803</v>
-      </c>
-      <c r="N98" s="0" t="s">
-        <v>804</v>
-      </c>
-      <c r="O98" s="0" t="s">
-        <v>805</v>
-      </c>
-      <c r="P98" s="0" t="s">
-        <v>806</v>
-      </c>
-      <c r="Q98" s="0" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
+        <v>803</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>804</v>
+      </c>
+      <c r="I99" s="0" t="s">
+        <v>805</v>
+      </c>
+      <c r="J99" s="0" t="s">
+        <v>806</v>
+      </c>
+      <c r="K99" s="0" t="s">
+        <v>807</v>
+      </c>
+      <c r="L99" s="0" t="s">
         <v>808</v>
       </c>
-      <c r="B99" s="0" t="s">
-        <v>248</v>
-      </c>
-      <c r="I99" s="0" t="s">
+      <c r="M99" s="0" t="s">
         <v>809</v>
       </c>
-      <c r="J99" s="0" t="s">
+      <c r="N99" s="0" t="s">
         <v>810</v>
       </c>
-      <c r="K99" s="0" t="s">
+      <c r="O99" s="0" t="s">
         <v>811</v>
       </c>
-      <c r="L99" s="0" t="s">
+      <c r="P99" s="0" t="s">
         <v>812</v>
       </c>
-      <c r="M99" s="0" t="s">
+      <c r="Q99" s="0" t="s">
         <v>813</v>
-      </c>
-      <c r="N99" s="0" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B100" s="0" t="s">
         <v>248</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="J100" s="0" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="K100" s="0" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="L100" s="0" t="s">
+        <v>818</v>
+      </c>
+      <c r="M100" s="0" t="s">
+        <v>819</v>
+      </c>
+      <c r="N100" s="0" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="0" t="s">
+        <v>821</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="I101" s="0" t="s">
+        <v>815</v>
+      </c>
+      <c r="J101" s="0" t="s">
         <v>816</v>
       </c>
-      <c r="M100" s="0" t="s">
+      <c r="K101" s="0" t="s">
         <v>817</v>
       </c>
-      <c r="N100" s="0" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
-        <v>819</v>
-      </c>
-      <c r="B101" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="E101" s="2" t="s">
+      <c r="L101" s="0" t="s">
         <v>822</v>
+      </c>
+      <c r="M101" s="0" t="s">
+        <v>823</v>
+      </c>
+      <c r="N101" s="0" t="s">
+        <v>824</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B102" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B103" s="0" t="s">
         <v>18</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="F103" s="0" t="s">
-        <v>831</v>
-      </c>
-      <c r="G103" s="0" t="s">
         <v>832</v>
       </c>
-      <c r="H103" s="0" t="s">
+    </row>
+    <row r="104" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="0" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="104" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="B104" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="B104" s="0" t="s">
+      <c r="D104" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="F104" s="0" t="s">
+        <v>837</v>
+      </c>
+      <c r="G104" s="0" t="s">
+        <v>838</v>
+      </c>
+      <c r="H104" s="0" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="0" t="s">
+        <v>840</v>
+      </c>
+      <c r="B105" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>835</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="I104" s="2" t="s">
-        <v>838</v>
-      </c>
-      <c r="J104" s="2" t="s">
-        <v>839</v>
-      </c>
-      <c r="K104" s="2" t="s">
-        <v>840</v>
-      </c>
-      <c r="L104" s="0" t="s">
+      <c r="C105" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="M104" s="0" t="s">
+      <c r="D105" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="N104" s="0" t="s">
+      <c r="E105" s="2" t="s">
         <v>843</v>
       </c>
-      <c r="O104" s="0" t="s">
+      <c r="I105" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="P104" s="0" t="s">
+      <c r="J105" s="2" t="s">
         <v>845</v>
       </c>
-      <c r="Q104" s="0" t="s">
+      <c r="K105" s="2" t="s">
         <v>846</v>
       </c>
-    </row>
-    <row r="105" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+      <c r="L105" s="0" t="s">
         <v>847</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="M105" s="0" t="s">
+        <v>848</v>
+      </c>
+      <c r="N105" s="0" t="s">
+        <v>849</v>
+      </c>
+      <c r="O105" s="0" t="s">
+        <v>850</v>
+      </c>
+      <c r="P105" s="0" t="s">
+        <v>851</v>
+      </c>
+      <c r="Q105" s="0" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="0" t="s">
+        <v>853</v>
+      </c>
+      <c r="B106" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
-        <v>851</v>
-      </c>
-      <c r="B106" s="0" t="s">
-        <v>658</v>
-      </c>
       <c r="C106" s="2" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>856</v>
+        <v>664</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>861</v>
+        <v>862</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>865</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>687</v>
-      </c>
-      <c r="L109" s="0" t="s">
-        <v>863</v>
-      </c>
-      <c r="M109" s="0" t="s">
-        <v>864</v>
-      </c>
-      <c r="N109" s="0" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>867</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>868</v>
-      </c>
-      <c r="D110" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="L110" s="0" t="s">
         <v>869</v>
       </c>
-      <c r="E110" s="2" t="s">
+      <c r="M110" s="0" t="s">
         <v>870</v>
       </c>
-      <c r="I110" s="2" t="s">
+      <c r="N110" s="0" t="s">
         <v>871</v>
-      </c>
-      <c r="J110" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="K110" s="2" t="s">
-        <v>873</v>
-      </c>
-      <c r="L110" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="M110" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="N110" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="O110" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="P110" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="Q110" s="2" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
+        <v>872</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>873</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="L111" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="M111" s="2" t="s">
         <v>881</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="N111" s="2" t="s">
         <v>882</v>
       </c>
-      <c r="D111" s="2" t="s">
+      <c r="O111" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="E111" s="2" t="s">
+      <c r="P111" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="I111" s="2" t="s">
+      <c r="Q111" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="J111" s="2" t="s">
+    </row>
+    <row r="112" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="0" t="s">
         <v>886</v>
       </c>
-      <c r="K111" s="2" t="s">
+      <c r="B112" s="0" t="s">
         <v>887</v>
       </c>
-      <c r="L111" s="0" t="s">
+      <c r="C112" s="2" t="s">
         <v>888</v>
       </c>
-      <c r="M111" s="0" t="s">
+      <c r="D112" s="2" t="s">
         <v>889</v>
       </c>
-      <c r="N111" s="0" t="s">
+      <c r="E112" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="O111" s="2" t="s">
+      <c r="I112" s="2" t="s">
         <v>891</v>
       </c>
-      <c r="P111" s="2" t="s">
+      <c r="J112" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="Q111" s="2" t="s">
+      <c r="K112" s="2" t="s">
         <v>893</v>
       </c>
-    </row>
-    <row r="112" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="s">
+      <c r="L112" s="0" t="s">
         <v>894</v>
       </c>
-      <c r="B112" s="0" t="s">
+      <c r="M112" s="0" t="s">
+        <v>895</v>
+      </c>
+      <c r="N112" s="0" t="s">
+        <v>896</v>
+      </c>
+      <c r="O112" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="P112" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="Q112" s="2" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="0" t="s">
+        <v>900</v>
+      </c>
+      <c r="B113" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>895</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>897</v>
-      </c>
-      <c r="I112" s="2" t="s">
-        <v>898</v>
-      </c>
-      <c r="J112" s="2" t="s">
-        <v>899</v>
-      </c>
-      <c r="K112" s="2" t="s">
-        <v>900</v>
-      </c>
-      <c r="L112" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="M112" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="N112" s="2" t="s">
+      <c r="C113" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="N113" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="O112" s="0" t="s">
-        <v>901</v>
-      </c>
-      <c r="P112" s="0" t="s">
-        <v>902</v>
-      </c>
-      <c r="Q112" s="0" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="s">
-        <v>904</v>
-      </c>
-      <c r="B113" s="0" t="s">
-        <v>867</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>905</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>906</v>
-      </c>
-      <c r="E113" s="2" t="s">
+      <c r="O113" s="0" t="s">
         <v>907</v>
       </c>
-      <c r="I113" s="2" t="s">
+      <c r="P113" s="0" t="s">
         <v>908</v>
       </c>
-      <c r="J113" s="2" t="s">
+      <c r="Q113" s="0" t="s">
         <v>909</v>
       </c>
-      <c r="K113" s="2" t="s">
+    </row>
+    <row r="114" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="0" t="s">
         <v>910</v>
       </c>
-      <c r="L113" s="0" t="s">
+      <c r="B114" s="0" t="s">
+        <v>873</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>911</v>
       </c>
-      <c r="M113" s="0" t="s">
+      <c r="D114" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="N113" s="0" t="s">
+      <c r="E114" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="O113" s="2" t="s">
+      <c r="I114" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="P113" s="2" t="s">
+      <c r="J114" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="Q113" s="2" t="s">
+      <c r="K114" s="2" t="s">
         <v>916</v>
       </c>
-    </row>
-    <row r="114" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="s">
+      <c r="L114" s="0" t="s">
         <v>917</v>
       </c>
-      <c r="B114" s="0" t="s">
+      <c r="M114" s="0" t="s">
         <v>918</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="N114" s="0" t="s">
         <v>919</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="O114" s="2" t="s">
         <v>920</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="P114" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="I114" s="0" t="s">
+      <c r="Q114" s="2" t="s">
         <v>922</v>
       </c>
-      <c r="J114" s="0" t="s">
+    </row>
+    <row r="115" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0" t="s">
         <v>923</v>
       </c>
-      <c r="K114" s="0" t="s">
+      <c r="B115" s="0" t="s">
         <v>924</v>
       </c>
-      <c r="L114" s="0" t="s">
+      <c r="C115" s="2" t="s">
         <v>925</v>
       </c>
-      <c r="M114" s="2" t="s">
+      <c r="D115" s="2" t="s">
         <v>926</v>
       </c>
-      <c r="N114" s="0" t="s">
+      <c r="E115" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="O114" s="0" t="s">
+      <c r="I115" s="0" t="s">
         <v>928</v>
       </c>
-      <c r="P114" s="0" t="s">
+      <c r="J115" s="0" t="s">
         <v>929</v>
       </c>
-      <c r="Q114" s="0" t="s">
+      <c r="K115" s="0" t="s">
         <v>930</v>
       </c>
-    </row>
-    <row r="115" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
+      <c r="L115" s="0" t="s">
         <v>931</v>
       </c>
-      <c r="B115" s="0" t="s">
+      <c r="M115" s="2" t="s">
         <v>932</v>
       </c>
-      <c r="I115" s="2" t="s">
+      <c r="N115" s="0" t="s">
         <v>933</v>
       </c>
-      <c r="J115" s="2" t="s">
+      <c r="O115" s="0" t="s">
         <v>934</v>
       </c>
-      <c r="K115" s="2" t="s">
+      <c r="P115" s="0" t="s">
         <v>935</v>
       </c>
-      <c r="L115" s="0" t="s">
+      <c r="Q115" s="0" t="s">
         <v>936</v>
-      </c>
-      <c r="M115" s="0" t="s">
-        <v>937</v>
-      </c>
-      <c r="N115" s="0" t="s">
-        <v>938</v>
-      </c>
-      <c r="O115" s="2" t="s">
-        <v>939</v>
-      </c>
-      <c r="P115" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="Q115" s="2" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
+        <v>937</v>
+      </c>
+      <c r="B116" s="0" t="s">
+        <v>938</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="L116" s="0" t="s">
         <v>942</v>
       </c>
-      <c r="B116" s="0" t="s">
-        <v>932</v>
-      </c>
-      <c r="I116" s="2" t="s">
+      <c r="M116" s="0" t="s">
         <v>943</v>
       </c>
-      <c r="J116" s="2" t="s">
+      <c r="N116" s="0" t="s">
         <v>944</v>
       </c>
-      <c r="K116" s="2" t="s">
+      <c r="O116" s="2" t="s">
         <v>945</v>
       </c>
-      <c r="L116" s="0" t="s">
+      <c r="P116" s="2" t="s">
         <v>946</v>
       </c>
-      <c r="M116" s="0" t="s">
+      <c r="Q116" s="2" t="s">
         <v>947</v>
       </c>
-      <c r="N116" s="0" t="s">
+    </row>
+    <row r="117" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="0" t="s">
         <v>948</v>
       </c>
-      <c r="O116" s="2" t="s">
+      <c r="B117" s="0" t="s">
+        <v>938</v>
+      </c>
+      <c r="I117" s="2" t="s">
         <v>949</v>
       </c>
-      <c r="P116" s="2" t="s">
+      <c r="J117" s="2" t="s">
         <v>950</v>
       </c>
-      <c r="Q116" s="2" t="s">
+      <c r="K117" s="2" t="s">
         <v>951</v>
       </c>
-    </row>
-    <row r="117" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="s">
+      <c r="L117" s="0" t="s">
         <v>952</v>
       </c>
-      <c r="B117" s="0" t="s">
-        <v>918</v>
-      </c>
-      <c r="C117" s="2" t="s">
+      <c r="M117" s="0" t="s">
         <v>953</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="N117" s="0" t="s">
         <v>954</v>
       </c>
-      <c r="E117" s="2" t="s">
+      <c r="O117" s="2" t="s">
         <v>955</v>
       </c>
-      <c r="I117" s="0" t="s">
+      <c r="P117" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="J117" s="0" t="s">
+      <c r="Q117" s="2" t="s">
         <v>957</v>
-      </c>
-      <c r="K117" s="0" t="s">
-        <v>958</v>
-      </c>
-      <c r="L117" s="0" t="s">
-        <v>959</v>
-      </c>
-      <c r="M117" s="0" t="s">
-        <v>960</v>
-      </c>
-      <c r="N117" s="0" t="s">
-        <v>961</v>
-      </c>
-      <c r="O117" s="0" t="s">
-        <v>962</v>
-      </c>
-      <c r="P117" s="0" t="s">
-        <v>963</v>
-      </c>
-      <c r="Q117" s="0" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
+        <v>958</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>924</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="I118" s="0" t="s">
+        <v>962</v>
+      </c>
+      <c r="J118" s="0" t="s">
+        <v>963</v>
+      </c>
+      <c r="K118" s="0" t="s">
+        <v>964</v>
+      </c>
+      <c r="L118" s="0" t="s">
         <v>965</v>
       </c>
-      <c r="B118" s="0" t="s">
-        <v>243</v>
-      </c>
-      <c r="C118" s="2" t="s">
+      <c r="M118" s="0" t="s">
         <v>966</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="N118" s="0" t="s">
         <v>967</v>
       </c>
-      <c r="E118" s="2" t="s">
+      <c r="O118" s="0" t="s">
         <v>968</v>
       </c>
-      <c r="I118" s="2" t="s">
+      <c r="P118" s="0" t="s">
         <v>969</v>
       </c>
-      <c r="J118" s="2" t="s">
+      <c r="Q118" s="0" t="s">
         <v>970</v>
-      </c>
-      <c r="K118" s="2" t="s">
-        <v>971</v>
-      </c>
-      <c r="L118" s="0" t="s">
-        <v>972</v>
-      </c>
-      <c r="M118" s="0" t="s">
-        <v>973</v>
-      </c>
-      <c r="N118" s="0" t="s">
-        <v>974</v>
-      </c>
-      <c r="O118" s="0" t="s">
-        <v>975</v>
-      </c>
-      <c r="P118" s="0" t="s">
-        <v>963</v>
-      </c>
-      <c r="Q118" s="0" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
+        <v>971</v>
+      </c>
+      <c r="B119" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="J119" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="B119" s="0" t="s">
+      <c r="K119" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="L119" s="0" t="s">
+        <v>978</v>
+      </c>
+      <c r="M119" s="0" t="s">
+        <v>979</v>
+      </c>
+      <c r="N119" s="0" t="s">
+        <v>980</v>
+      </c>
+      <c r="O119" s="0" t="s">
+        <v>981</v>
+      </c>
+      <c r="P119" s="0" t="s">
+        <v>969</v>
+      </c>
+      <c r="Q119" s="0" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="0" t="s">
+        <v>982</v>
+      </c>
+      <c r="B120" s="0" t="s">
         <v>432</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>977</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>979</v>
-      </c>
-      <c r="I119" s="0" t="s">
-        <v>980</v>
-      </c>
-      <c r="J119" s="0" t="s">
-        <v>981</v>
-      </c>
-      <c r="K119" s="0" t="s">
-        <v>982</v>
-      </c>
-      <c r="L119" s="0" t="s">
+      <c r="C120" s="2" t="s">
         <v>983</v>
       </c>
-      <c r="M119" s="0" t="s">
+      <c r="D120" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="N119" s="0" t="s">
+      <c r="E120" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="O119" s="0" t="s">
+      <c r="I120" s="0" t="s">
         <v>986</v>
       </c>
-      <c r="P119" s="0" t="s">
+      <c r="J120" s="0" t="s">
         <v>987</v>
       </c>
-      <c r="Q119" s="0" t="s">
+      <c r="K120" s="0" t="s">
         <v>988</v>
       </c>
-    </row>
-    <row r="120" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
+      <c r="L120" s="0" t="s">
         <v>989</v>
       </c>
-      <c r="B120" s="0" t="s">
+      <c r="M120" s="0" t="s">
+        <v>990</v>
+      </c>
+      <c r="N120" s="0" t="s">
+        <v>991</v>
+      </c>
+      <c r="O120" s="0" t="s">
+        <v>992</v>
+      </c>
+      <c r="P120" s="0" t="s">
+        <v>993</v>
+      </c>
+      <c r="Q120" s="0" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="0" t="s">
+        <v>995</v>
+      </c>
+      <c r="B121" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="C120" s="2" t="s">
-        <v>990</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>991</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>992</v>
-      </c>
-      <c r="I120" s="0" t="s">
-        <v>993</v>
-      </c>
-      <c r="J120" s="0" t="s">
-        <v>994</v>
-      </c>
-      <c r="K120" s="0" t="s">
-        <v>995</v>
-      </c>
-      <c r="L120" s="0" t="s">
+      <c r="C121" s="2" t="s">
         <v>996</v>
       </c>
-      <c r="M120" s="0" t="s">
+      <c r="D121" s="2" t="s">
         <v>997</v>
       </c>
-      <c r="N120" s="0" t="s">
+      <c r="E121" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="O120" s="0" t="s">
+      <c r="I121" s="0" t="s">
         <v>999</v>
       </c>
-      <c r="P120" s="0" t="s">
+      <c r="J121" s="0" t="s">
         <v>1000</v>
       </c>
-      <c r="Q120" s="0" t="s">
+      <c r="K121" s="0" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="121" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
+      <c r="L121" s="0" t="s">
         <v>1002</v>
       </c>
-      <c r="B121" s="0" t="s">
+      <c r="M121" s="0" t="s">
         <v>1003</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="N121" s="0" t="s">
         <v>1004</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="O121" s="0" t="s">
         <v>1005</v>
       </c>
-      <c r="E121" s="2" t="s">
+      <c r="P121" s="0" t="s">
         <v>1006</v>
       </c>
-      <c r="I121" s="2" t="s">
+      <c r="Q121" s="0" t="s">
         <v>1007</v>
       </c>
-      <c r="J121" s="2" t="s">
+    </row>
+    <row r="122" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="0" t="s">
         <v>1008</v>
       </c>
-      <c r="K121" s="2" t="s">
+      <c r="B122" s="0" t="s">
         <v>1009</v>
       </c>
-      <c r="L121" s="2" t="s">
+      <c r="C122" s="2" t="s">
         <v>1010</v>
       </c>
-      <c r="M121" s="2" t="s">
+      <c r="D122" s="2" t="s">
         <v>1011</v>
       </c>
-      <c r="N121" s="2" t="s">
+      <c r="E122" s="2" t="s">
         <v>1012</v>
       </c>
-      <c r="O121" s="2" t="s">
+      <c r="I122" s="2" t="s">
         <v>1013</v>
       </c>
-      <c r="P121" s="2" t="s">
+      <c r="J122" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="Q121" s="2" t="s">
+      <c r="K122" s="2" t="s">
         <v>1015</v>
       </c>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
+      <c r="L122" s="2" t="s">
         <v>1016</v>
       </c>
-      <c r="B122" s="0" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C122" s="0" t="s">
+      <c r="M122" s="2" t="s">
         <v>1017</v>
       </c>
-      <c r="D122" s="0" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E122" s="0" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N122" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="O122" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="P122" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="Q122" s="2" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>1017</v>
-      </c>
-      <c r="I123" s="0" t="s">
-        <v>1019</v>
-      </c>
-      <c r="J123" s="0" t="s">
-        <v>1020</v>
-      </c>
-      <c r="K123" s="0" t="s">
-        <v>1021</v>
-      </c>
-      <c r="L123" s="0" t="s">
-        <v>1022</v>
-      </c>
-      <c r="M123" s="0" t="s">
         <v>1023</v>
       </c>
-      <c r="N123" s="0" t="s">
+    </row>
+    <row r="124" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="0" t="s">
         <v>1024</v>
       </c>
-      <c r="O123" s="2" t="s">
+      <c r="B124" s="0" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C124" s="0" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D124" s="0" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E124" s="0" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I124" s="0" t="s">
         <v>1025</v>
       </c>
-      <c r="P123" s="2" t="s">
+      <c r="J124" s="0" t="s">
         <v>1026</v>
       </c>
-      <c r="Q123" s="2" t="s">
+      <c r="K124" s="0" t="s">
         <v>1027</v>
       </c>
-    </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="s">
+      <c r="L124" s="0" t="s">
         <v>1028</v>
       </c>
-      <c r="B124" s="0" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C124" s="0" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D124" s="0" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E124" s="0" t="s">
-        <v>1017</v>
-      </c>
-      <c r="I124" s="0" t="s">
+      <c r="M124" s="0" t="s">
         <v>1029</v>
       </c>
-      <c r="J124" s="0" t="s">
+      <c r="N124" s="0" t="s">
         <v>1030</v>
       </c>
-      <c r="K124" s="0" t="s">
+      <c r="O124" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="L124" s="0" t="s">
+      <c r="P124" s="2" t="s">
         <v>1032</v>
       </c>
-      <c r="M124" s="0" t="s">
+      <c r="Q124" s="2" t="s">
         <v>1033</v>
       </c>
-      <c r="N124" s="0" t="s">
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="0" t="s">
         <v>1034</v>
       </c>
-      <c r="O124" s="0" t="s">
+      <c r="B125" s="0" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C125" s="0" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D125" s="0" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E125" s="0" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I125" s="0" t="s">
         <v>1035</v>
       </c>
-      <c r="P124" s="0" t="s">
+      <c r="J125" s="0" t="s">
         <v>1036</v>
       </c>
-      <c r="Q124" s="0" t="s">
+      <c r="K125" s="0" t="s">
         <v>1037</v>
       </c>
-    </row>
-    <row r="125" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="s">
+      <c r="L125" s="0" t="s">
         <v>1038</v>
       </c>
-      <c r="B125" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C125" s="0" t="s">
+      <c r="M125" s="0" t="s">
         <v>1039</v>
       </c>
-      <c r="D125" s="0" t="s">
+      <c r="N125" s="0" t="s">
         <v>1040</v>
       </c>
-      <c r="E125" s="0" t="s">
+      <c r="O125" s="0" t="s">
         <v>1041</v>
       </c>
-      <c r="L125" s="0" t="s">
+      <c r="P125" s="0" t="s">
         <v>1042</v>
       </c>
-      <c r="M125" s="0" t="s">
+      <c r="Q125" s="0" t="s">
         <v>1043</v>
       </c>
-      <c r="N125" s="0" t="s">
+    </row>
+    <row r="126" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="0" t="s">
         <v>1044</v>
-      </c>
-      <c r="O125" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="P125" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="Q125" s="2" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="s">
-        <v>1048</v>
       </c>
       <c r="B126" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="0" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D126" s="0" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E126" s="0" t="s">
+        <v>1047</v>
+      </c>
+      <c r="L126" s="0" t="s">
+        <v>1048</v>
+      </c>
+      <c r="M126" s="0" t="s">
         <v>1049</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="N126" s="0" t="s">
         <v>1050</v>
       </c>
-      <c r="E126" s="2" t="s">
+      <c r="O126" s="2" t="s">
         <v>1051</v>
       </c>
-      <c r="L126" s="0" t="s">
+      <c r="P126" s="2" t="s">
         <v>1052</v>
       </c>
-      <c r="M126" s="0" t="s">
+      <c r="Q126" s="2" t="s">
         <v>1053</v>
       </c>
-      <c r="N126" s="0" t="s">
+    </row>
+    <row r="127" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="0" t="s">
         <v>1054</v>
       </c>
-    </row>
-    <row r="127" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="s">
+      <c r="B127" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C127" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="B127" s="0" t="s">
+      <c r="D127" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="C127" s="2" t="s">
+      <c r="E127" s="2" t="s">
         <v>1057</v>
       </c>
-      <c r="D127" s="2" t="s">
+      <c r="L127" s="0" t="s">
         <v>1058</v>
       </c>
-      <c r="E127" s="2" t="s">
+      <c r="M127" s="0" t="s">
         <v>1059</v>
       </c>
-      <c r="I127" s="2" t="s">
+      <c r="N127" s="0" t="s">
         <v>1060</v>
       </c>
-      <c r="J127" s="2" t="s">
+    </row>
+    <row r="128" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="0" t="s">
         <v>1061</v>
       </c>
-      <c r="K127" s="2" t="s">
+      <c r="B128" s="0" t="s">
         <v>1062</v>
       </c>
-      <c r="L127" s="2" t="s">
+      <c r="C128" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="M127" s="2" t="s">
+      <c r="D128" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="N127" s="2" t="s">
+      <c r="E128" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="O127" s="2" t="s">
+      <c r="I128" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="P127" s="2" t="s">
+      <c r="J128" s="2" t="s">
         <v>1067</v>
       </c>
-      <c r="Q127" s="2" t="s">
+      <c r="K128" s="2" t="s">
         <v>1068</v>
       </c>
-    </row>
-    <row r="128" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="s">
+      <c r="L128" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="B128" s="0" t="s">
+      <c r="M128" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="N128" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="O128" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="P128" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="Q128" s="2" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="0" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B129" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C128" s="2" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>1072</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>1073</v>
-      </c>
-      <c r="J128" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="K128" s="2" t="s">
-        <v>1075</v>
-      </c>
-      <c r="L128" s="0" t="s">
+      <c r="C129" s="2" t="s">
         <v>1076</v>
       </c>
-      <c r="M128" s="0" t="s">
+      <c r="D129" s="2" t="s">
         <v>1077</v>
       </c>
-      <c r="N128" s="0" t="s">
+      <c r="E129" s="2" t="s">
         <v>1078</v>
       </c>
-      <c r="O128" s="2" t="s">
+      <c r="I129" s="2" t="s">
         <v>1079</v>
       </c>
-      <c r="P128" s="2" t="s">
+      <c r="J129" s="2" t="s">
         <v>1080</v>
       </c>
-      <c r="Q128" s="2" t="s">
+      <c r="K129" s="2" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="129" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="s">
+      <c r="L129" s="0" t="s">
         <v>1082</v>
       </c>
-      <c r="B129" s="0" t="s">
+      <c r="M129" s="0" t="s">
         <v>1083</v>
       </c>
-      <c r="C129" s="2" t="s">
+      <c r="N129" s="0" t="s">
         <v>1084</v>
       </c>
-      <c r="D129" s="2" t="s">
+      <c r="O129" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="E129" s="2" t="s">
+      <c r="P129" s="2" t="s">
         <v>1086</v>
       </c>
-      <c r="I129" s="2" t="s">
+      <c r="Q129" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="J129" s="2" t="s">
+    </row>
+    <row r="130" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="0" t="s">
         <v>1088</v>
       </c>
-      <c r="K129" s="2" t="s">
+      <c r="B130" s="0" t="s">
         <v>1089</v>
       </c>
-      <c r="L129" s="0" t="s">
+      <c r="C130" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="M129" s="0" t="s">
+      <c r="D130" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="N129" s="0" t="s">
+      <c r="E130" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="O129" s="2" t="s">
+      <c r="I130" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="P129" s="2" t="s">
+      <c r="J130" s="2" t="s">
         <v>1094</v>
       </c>
-      <c r="Q129" s="2" t="s">
+      <c r="K130" s="2" t="s">
         <v>1095</v>
       </c>
-    </row>
-    <row r="130" customFormat="false" ht="153.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0" t="s">
+      <c r="L130" s="0" t="s">
         <v>1096</v>
       </c>
-      <c r="B130" s="0" t="s">
+      <c r="M130" s="0" t="s">
         <v>1097</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="N130" s="0" t="s">
         <v>1098</v>
       </c>
-      <c r="D130" s="2" t="s">
+      <c r="O130" s="2" t="s">
         <v>1099</v>
       </c>
-      <c r="E130" s="2" t="s">
+      <c r="P130" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="I130" s="2" t="s">
+      <c r="Q130" s="2" t="s">
         <v>1101</v>
       </c>
-      <c r="J130" s="2" t="s">
+    </row>
+    <row r="131" customFormat="false" ht="153.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="0" t="s">
         <v>1102</v>
       </c>
-      <c r="K130" s="2" t="s">
+      <c r="B131" s="0" t="s">
         <v>1103</v>
       </c>
-      <c r="L130" s="2" t="s">
+      <c r="C131" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="M130" s="2" t="s">
+      <c r="D131" s="2" t="s">
         <v>1105</v>
       </c>
-      <c r="N130" s="2" t="s">
+      <c r="E131" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="O130" s="2" t="s">
+      <c r="I131" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="P130" s="2" t="s">
+      <c r="J131" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="Q130" s="2" t="s">
+      <c r="K131" s="2" t="s">
         <v>1109</v>
       </c>
-    </row>
-    <row r="131" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="s">
+      <c r="L131" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="B131" s="0" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C131" s="2" t="s">
+      <c r="M131" s="2" t="s">
         <v>1111</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="N131" s="2" t="s">
         <v>1112</v>
       </c>
-      <c r="E131" s="2" t="s">
+      <c r="O131" s="2" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P131" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="Q131" s="2" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="B132" s="0" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="0" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B133" s="0" t="s">
         <v>243</v>
       </c>
-      <c r="I132" s="0" t="s">
-        <v>1115</v>
-      </c>
-      <c r="J132" s="0" t="s">
-        <v>1116</v>
-      </c>
-      <c r="K132" s="0" t="s">
-        <v>1117</v>
-      </c>
-      <c r="L132" s="0" t="s">
-        <v>1118</v>
-      </c>
-      <c r="M132" s="0" t="s">
-        <v>1119</v>
-      </c>
-      <c r="N132" s="0" t="s">
-        <v>693</v>
-      </c>
-      <c r="O132" s="0" t="s">
-        <v>1120</v>
-      </c>
-      <c r="P132" s="0" t="s">
+      <c r="I133" s="0" t="s">
         <v>1121</v>
       </c>
-      <c r="Q132" s="0" t="s">
+      <c r="J133" s="0" t="s">
         <v>1122</v>
+      </c>
+      <c r="K133" s="0" t="s">
+        <v>1123</v>
+      </c>
+      <c r="L133" s="0" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M133" s="0" t="s">
+        <v>1125</v>
+      </c>
+      <c r="N133" s="0" t="s">
+        <v>699</v>
+      </c>
+      <c r="O133" s="0" t="s">
+        <v>1126</v>
+      </c>
+      <c r="P133" s="0" t="s">
+        <v>1127</v>
+      </c>
+      <c r="Q133" s="0" t="s">
+        <v>1128</v>
       </c>
     </row>
   </sheetData>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/CharaText.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="1129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="1142">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">black_angel</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.338 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve"> *파닥파닥*
@@ -185,7 +185,7 @@
   <si>
     <t xml:space="preserve"> *パタパタ*
  * ばさっばさっ*
- *ハタハタ*</t>
+*ハタハタ*</t>
   </si>
   <si>
     <t xml:space="preserve">「꺄아!」</t>
@@ -250,7 +250,7 @@
   <si>
     <t xml:space="preserve">"No way!"
 "I's a bitter tirade."
-"Did I suck that bad?" </t>
+"Did I suck that bad?"</t>
   </si>
   <si>
     <t xml:space="preserve">「そんな馬鹿な…」
@@ -627,7 +627,7 @@
     <t xml:space="preserve">「うみみゃ」
 「みゅー」
 「みゃ」
- *ごろごろ*</t>
+*ごろごろ*</t>
   </si>
   <si>
     <t xml:space="preserve">「후캬악!」
@@ -666,7 +666,7 @@
   <si>
     <t xml:space="preserve">All around you is the sensation of being in a sacred place.
 You have seldom felt such an air of peace.
-All around is very quiet  yet you aren't the least bit lonely.
+All around is very quiet, yet you aren't the least bit lonely.
 In your mind you hear the strange echoes of a voice in prayer.</t>
   </si>
   <si>
@@ -1465,7 +1465,7 @@
   </si>
   <si>
     <t xml:space="preserve">「이 소식을… 팔미아에…」
-「 …으, 으윽 」</t>
+「…으, 으윽 」</t>
   </si>
   <si>
     <t xml:space="preserve">"Ugh..."
@@ -1473,7 +1473,7 @@
   </si>
   <si>
     <t xml:space="preserve">「この知らせを…パルミアに…」
-「 …う、うぅ 」</t>
+「…う、うぅ 」</t>
   </si>
   <si>
     <t xml:space="preserve">「이거야 원, 끝났구만」
@@ -2314,7 +2314,7 @@
 「크크크…」</t>
   </si>
   <si>
-    <t xml:space="preserve">"Heh  easy money."
+    <t xml:space="preserve">"Heh, easy money."
 "Time to pluck it."
 "Heh heh heh..."</t>
   </si>
@@ -2446,9 +2446,9 @@
   </si>
   <si>
     <t xml:space="preserve">「いい湯{だ}」
-「 次はどこの温泉にしようかな」
+「次はどこの温泉にしようかな」
 「温泉から上がるとお腹が空くよね」 
-「 体がポカポカしてきた {のだ}」
+「体がポカポカしてきた {のだ}」
 水をパシャパシャする音が聞こえる。
 温泉の香りがする。</t>
   </si>
@@ -2911,7 +2911,7 @@
   </si>
   <si>
     <t xml:space="preserve">"Is it over already?"
-"That's unfortunate." </t>
+"That's unfortunate."</t>
   </si>
   <si>
     <t xml:space="preserve">「もう終わりか？」
@@ -2929,7 +2929,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">You are stunned by the face of a girl who as beautiful as an Elean.
+    <t xml:space="preserve">You are stunned by the face of a girl who is as beautiful as an Elean.
 "Do you know the fairy tale of the ugly beast?"
 "I hope Master Cetrus is alright..."
 "It was a nice break."
@@ -3364,7 +3364,7 @@
     <t xml:space="preserve">「파옹…」</t>
   </si>
   <si>
-    <t xml:space="preserve">"Toot..." </t>
+    <t xml:space="preserve">"Toot..."</t>
   </si>
   <si>
     <t xml:space="preserve">「パオン…」</t>
@@ -3877,7 +3877,7 @@
     <t xml:space="preserve"> *ドスン*
 リトルシスター「見て#bigdaddy、天使がいるわ」
 リトルシスター「急いで#bigdaddy、空で天使が踊っているの！」
- *ドン*</t>
+*ドン*</t>
   </si>
   <si>
     <t xml:space="preserve">리틀 시스터「죽여! 죽여!」
@@ -4105,7 +4105,7 @@
   <si>
     <t xml:space="preserve">"What in the world!"
 "What are you doing!"
-"What is the meaning of this!" </t>
+"What is the meaning of this!"</t>
   </si>
   <si>
     <t xml:space="preserve">「なんということだ！」
@@ -4210,11 +4210,11 @@
 「風の旋律に耳を傾けよう」
 「この小さな薬瓶に&amp;世界の一片を閉じ込めよう」
 「ああ、この薬草の香り」
-「 星々の輝きは万病に効くんだ」
+「星々の輝きは万病に効くんだ」
 「ふふ、また道を間違えたかな？」
 「迷う旅もまた一つの冒険さ」
 「風の名前を知っているかい？」
-「 水の音は最も古い語り部だ」</t>
+「水の音は最も古い語り部だ」</t>
   </si>
   <si>
     <t xml:space="preserve">「싸움은 좋아하지 않지만…」
@@ -4564,7 +4564,7 @@
   <si>
     <t xml:space="preserve">「あんな極上の女はそうはいねえ」
 「俺の手に掛かれば、どんな女もイチコロよ」
- *レロレロレロ*
+*レロレロレロ*
 「まったく罪な男に生まれちまったもんだ」</t>
   </si>
   <si>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">「히양…」</t>
   </si>
   <si>
-    <t xml:space="preserve">" Ngh..."</t>
+    <t xml:space="preserve">"Ngh..."</t>
   </si>
   <si>
     <t xml:space="preserve">「ひゃん…」</t>
@@ -4779,6 +4779,66 @@
   </si>
   <si>
     <t xml:space="preserve">「私…さびついてしまったようです…」 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">adv_schwert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「…아직, 가동합니다」
+「주변 스캔——이상 없음」
+「명령 확인——」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"...Still operational."
+"Area scan—no anomalies detected."
+"Checking orders—"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「…まだ、稼働します」
+「周辺走査——異常なし」
+「命令を確認——」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「전투 프로토콜——실행」
+「무장 전개합니다」
+「적성 반응 발견」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Combat protocol—executing."
+"Deploying weapons."
+"Hostile signature detected."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「戦闘プロトコル——実行」
+「武装展開します」
+「敵性反応を発見」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「기억 영역——에러. 복원 불능」
+「마력 제어——에러. 재시도」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Memory sector—error. Recovery impossible."
+"Mana control—error. Retrying."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「記憶領域——エラー。復元不能」
+「魔力制御——エラー。再試行」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「자가 진단——개시」
+「마력로——안정 」
+「적의 소멸 확인」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Self-diagnostic—initiated."
+"Mana core—stable."
+"Hostile signature eliminated."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「自己診断——開始」
+「魔力炉——安定 」
+「敵の消滅を確認」</t>
   </si>
   <si>
     <t xml:space="preserve">adv_gaki</t>
@@ -4880,9 +4940,9 @@
   <si>
     <t xml:space="preserve">「影は、私の鏡」
 「暗闇は怖くない。君はどうかな？」
-「 この翼、触ってみる？ 」
-「 どこか遠くに行きたくなるわ」
-「 この世界は奇妙ね 」</t>
+「この翼、触ってみる？ 」
+「どこか遠くに行きたくなるわ」
+「この世界は奇妙ね 」</t>
   </si>
   <si>
     <t xml:space="preserve">「자 그림자여, 같이 춤춰보자」
@@ -4928,7 +4988,7 @@
     <t xml:space="preserve">「さよなら」
 「終わりよ」
 「私の世界へようこそ」
-「 闇に呑まれるがいい」 </t>
+「闇に呑まれるがいい」 </t>
   </si>
   <si>
     <t xml:space="preserve">adv_mesherada</t>
@@ -5407,7 +5467,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q133"/>
+  <dimension ref="A1:Q134"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="1" style="0" width="16.15"/>
@@ -6598,7 +6658,7 @@
         <v>308</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>309</v>
@@ -7507,7 +7567,7 @@
         <v>514</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>480</v>
+        <v>43</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>515</v>
@@ -9251,7 +9311,7 @@
         <v>910</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>873</v>
+        <v>43</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>911</v>
@@ -9790,56 +9850,56 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
         <v>1061</v>
       </c>
       <c r="B128" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>1062</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="D128" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="D128" s="2" t="s">
+      <c r="E128" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="E128" s="2" t="s">
+      <c r="I128" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="I128" s="2" t="s">
+      <c r="J128" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="J128" s="2" t="s">
+      <c r="K128" s="2" t="s">
         <v>1067</v>
       </c>
-      <c r="K128" s="2" t="s">
+      <c r="L128" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="L128" s="2" t="s">
+      <c r="M128" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="M128" s="2" t="s">
+      <c r="N128" s="2" t="s">
         <v>1070</v>
       </c>
-      <c r="N128" s="2" t="s">
+      <c r="O128" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="O128" s="2" t="s">
+      <c r="P128" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="P128" s="2" t="s">
+      <c r="Q128" s="2" t="s">
         <v>1073</v>
       </c>
-      <c r="Q128" s="2" t="s">
+    </row>
+    <row r="129" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="0" t="s">
         <v>1074</v>
       </c>
-    </row>
-    <row r="129" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="s">
+      <c r="B129" s="0" t="s">
         <v>1075</v>
-      </c>
-      <c r="B129" s="0" t="s">
-        <v>38</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>1076</v>
@@ -9859,13 +9919,13 @@
       <c r="K129" s="2" t="s">
         <v>1081</v>
       </c>
-      <c r="L129" s="0" t="s">
+      <c r="L129" s="2" t="s">
         <v>1082</v>
       </c>
-      <c r="M129" s="0" t="s">
+      <c r="M129" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="N129" s="0" t="s">
+      <c r="N129" s="2" t="s">
         <v>1084</v>
       </c>
       <c r="O129" s="2" t="s">
@@ -9878,100 +9938,100 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
         <v>1088</v>
       </c>
       <c r="B130" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="D130" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="D130" s="2" t="s">
+      <c r="E130" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="E130" s="2" t="s">
+      <c r="I130" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="I130" s="2" t="s">
+      <c r="J130" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="J130" s="2" t="s">
+      <c r="K130" s="2" t="s">
         <v>1094</v>
       </c>
-      <c r="K130" s="2" t="s">
+      <c r="L130" s="0" t="s">
         <v>1095</v>
       </c>
-      <c r="L130" s="0" t="s">
+      <c r="M130" s="0" t="s">
         <v>1096</v>
       </c>
-      <c r="M130" s="0" t="s">
+      <c r="N130" s="0" t="s">
         <v>1097</v>
       </c>
-      <c r="N130" s="0" t="s">
+      <c r="O130" s="2" t="s">
         <v>1098</v>
       </c>
-      <c r="O130" s="2" t="s">
+      <c r="P130" s="2" t="s">
         <v>1099</v>
       </c>
-      <c r="P130" s="2" t="s">
+      <c r="Q130" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="Q130" s="2" t="s">
+    </row>
+    <row r="131" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="0" t="s">
         <v>1101</v>
       </c>
-    </row>
-    <row r="131" customFormat="false" ht="153.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="s">
+      <c r="B131" s="0" t="s">
         <v>1102</v>
       </c>
-      <c r="B131" s="0" t="s">
+      <c r="C131" s="2" t="s">
         <v>1103</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="D131" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="E131" s="2" t="s">
         <v>1105</v>
       </c>
-      <c r="E131" s="2" t="s">
+      <c r="I131" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="I131" s="2" t="s">
+      <c r="J131" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="J131" s="2" t="s">
+      <c r="K131" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="K131" s="2" t="s">
+      <c r="L131" s="0" t="s">
         <v>1109</v>
       </c>
-      <c r="L131" s="2" t="s">
+      <c r="M131" s="0" t="s">
         <v>1110</v>
       </c>
-      <c r="M131" s="2" t="s">
+      <c r="N131" s="0" t="s">
         <v>1111</v>
       </c>
-      <c r="N131" s="2" t="s">
+      <c r="O131" s="2" t="s">
         <v>1112</v>
       </c>
-      <c r="O131" s="2" t="s">
+      <c r="P131" s="2" t="s">
         <v>1113</v>
       </c>
-      <c r="P131" s="2" t="s">
+      <c r="Q131" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="Q131" s="2" t="s">
+    </row>
+    <row r="132" customFormat="false" ht="153.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="0" t="s">
         <v>1115</v>
       </c>
-    </row>
-    <row r="132" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0" t="s">
+      <c r="B132" s="0" t="s">
         <v>1116</v>
-      </c>
-      <c r="B132" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>1117</v>
@@ -9982,40 +10042,84 @@
       <c r="E132" s="2" t="s">
         <v>1119</v>
       </c>
-    </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I132" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K132" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="L132" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="M132" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N132" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="O132" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="P132" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="Q132" s="2" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
       <c r="B133" s="0" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="0" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B134" s="0" t="s">
         <v>243</v>
       </c>
-      <c r="I133" s="0" t="s">
-        <v>1121</v>
-      </c>
-      <c r="J133" s="0" t="s">
-        <v>1122</v>
-      </c>
-      <c r="K133" s="0" t="s">
-        <v>1123</v>
-      </c>
-      <c r="L133" s="0" t="s">
-        <v>1124</v>
-      </c>
-      <c r="M133" s="0" t="s">
-        <v>1125</v>
-      </c>
-      <c r="N133" s="0" t="s">
+      <c r="I134" s="0" t="s">
+        <v>1134</v>
+      </c>
+      <c r="J134" s="0" t="s">
+        <v>1135</v>
+      </c>
+      <c r="K134" s="0" t="s">
+        <v>1136</v>
+      </c>
+      <c r="L134" s="0" t="s">
+        <v>1137</v>
+      </c>
+      <c r="M134" s="0" t="s">
+        <v>1138</v>
+      </c>
+      <c r="N134" s="0" t="s">
         <v>699</v>
       </c>
-      <c r="O133" s="0" t="s">
-        <v>1126</v>
-      </c>
-      <c r="P133" s="0" t="s">
-        <v>1127</v>
-      </c>
-      <c r="Q133" s="0" t="s">
-        <v>1128</v>
+      <c r="O134" s="0" t="s">
+        <v>1139</v>
+      </c>
+      <c r="P134" s="0" t="s">
+        <v>1140</v>
+      </c>
+      <c r="Q134" s="0" t="s">
+        <v>1141</v>
       </c>
     </row>
   </sheetData>
